--- a/Pillar4_Stock_Notes.xlsx
+++ b/Pillar4_Stock_Notes.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Comment Log'!$A$1:$D$1452</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Dashboard Notes'!$A$1:$C$38</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Follow-ups'!$A$1:$D$20</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Our Notes'!$A$1:$F$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Our Notes'!$A$1:$F$2</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Stock Index'!$A$1:$M$127</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6990" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6989" uniqueCount="1220">
   <si>
     <t xml:space="preserve">PILLAR 4 - US STOCK NOTES</t>
   </si>
@@ -3793,7 +3793,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3810,6 +3810,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -3862,7 +3868,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3911,6 +3917,10 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3924,7 +3934,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3952,6 +3962,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF006100"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -29945,7 +29963,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12"/>
@@ -29976,7 +29994,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -29995,23 +30013,13 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
         <v>1177</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>1177</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F2"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Pillar4_Stock_Notes.xlsx
+++ b/Pillar4_Stock_Notes.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Follow-ups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Index'!$A$1:$M$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Index'!$A$1:$M$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$262</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Full Log'!$A$1:$D$1470</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Our Notes'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Follow-ups'!$A$1:$D$20</definedName>
   </definedNames>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5640,17 +5640,17 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Affirm Holdings</t>
+          <t>Sterling Infrastructure</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
+          <t>Neocloud Watch</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr"/>
@@ -5658,42 +5658,34 @@
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="9" t="n"/>
       <c r="H92" s="9" t="n">
-        <v>79.56</v>
+        <v>547.0599999999999</v>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J92" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A92)</f>
         <v/>
       </c>
-      <c r="K92" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr"/>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Affirm Holdings</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -5706,11 +5698,11 @@
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="9" t="n"/>
       <c r="H93" s="9" t="n">
-        <v>152.89</v>
+        <v>79.56</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="J93" s="5">
@@ -5724,24 +5716,24 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
-          <t>The dangerous category — and this is the one worth knowing about. StockTwits, CNN Business, Simply Wall St and TradingView all hand me a price with no date attached to it. That is far more dangerous than a site that fails, because a wrong number that looks confident is indistinguishable from a right one. I have a rule now: no date stamp, no use. TradingKey deserves special mention — it has correct dates but its percentage moves are simply wrong (it showed COIN at −8.03% when the real move was −10.59%), so you can't work backwards from it either.</t>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -5754,7 +5746,7 @@
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="9" t="n"/>
       <c r="H94" s="9" t="n">
-        <v>52.41</v>
+        <v>152.89</v>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
@@ -5772,24 +5764,24 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Two things, and the first is a housekeeping error on our side: the ticker is no longer FI. Fiserv moved to Nasdaq and changed to FISV (announced October 29, 2025). Our board still carries it as FI, which means the quote we've been showing may not be reliably matched. I'll correct that on the next push.</t>
+          <t>The dangerous category — and this is the one worth knowing about. StockTwits, CNN Business, Simply Wall St and TradingView all hand me a price with no date attached to it. That is far more dangerous than a site that fails, because a wrong number that looks confident is indistinguishable from a right one. I have a rule now: no date stamp, no use. TradingKey deserves special mention — it has correct dates but its percentage moves are simply wrong (it showed COIN at −8.03% when the real move was −10.59%), so you can't work backwards from it either.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Robinhood Markets</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -5802,7 +5794,7 @@
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="9" t="n"/>
       <c r="H95" s="9" t="n">
-        <v>93.29000000000001</v>
+        <v>52.41</v>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
@@ -5815,29 +5807,29 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>The honest bear case: Robinhood trades at 16.5× its revenue against a historical average of 11.9×. If it simply drifts back to its own normal valuation, that's 30%+ downside with nothing else going wrong. And its earnings depend on retail investors trading actively — in a dull market, that dries up fast.</t>
+          <t>⚠️ Two things, and the first is a housekeeping error on our side: the ticker is no longer FI. Fiserv moved to Nasdaq and changed to FISV (announced October 29, 2025). Our board still carries it as FI, which means the quote we've been showing may not be reliably matched. I'll correct that on the next push.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Lemonade</t>
+          <t>Robinhood Markets</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -5850,11 +5842,11 @@
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="9" t="n"/>
       <c r="H96" s="9" t="n">
-        <v>51.86</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J96" s="5">
@@ -5863,29 +5855,29 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>One number I couldn't double-check. AIRJ's $5.84 close comes from a single source. The usual quote page was serving a mid-afternoon snapshot rather than the closing price, and no other free source had Aug 4 data for it. Everything else is corroborated — Lemonade's $54.11 was confirmed by two independent sources after the first two disagreed, and Hinge's $79.42 was confirmed by a news article quoting the same figure.</t>
+          <t>The honest bear case: Robinhood trades at 16.5× its revenue against a historical average of 11.9×. If it simply drifts back to its own normal valuation, that's 30%+ downside with nothing else going wrong. And its earnings depend on retail investors trading actively — in a dull market, that dries up fast.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Lemonade</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -5898,11 +5890,11 @@
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="9" t="n"/>
       <c r="H97" s="9" t="n">
-        <v>562.95</v>
+        <v>51.86</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J97" s="5">
@@ -5911,29 +5903,29 @@
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
-          <t>| Compounders | MA | Mastercard | 27 | +17% | 46% | 100% gross margin, ROE 232% — elite |</t>
+          <t>One number I couldn't double-check. AIRJ's $5.84 close comes from a single source. The usual quote page was serving a mid-afternoon snapshot rather than the closing price, and no other free source had Aug 4 data for it. Everything else is corroborated — Lemonade's $54.11 was confirmed by two independent sources after the first two disagreed, and Hinge's $79.42 was confirmed by a news article quoting the same figure.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>MercadoLibre</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -5946,7 +5938,7 @@
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="9" t="n"/>
       <c r="H98" s="9" t="n">
-        <v>1820.69</v>
+        <v>562.95</v>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
@@ -5959,29 +5951,29 @@
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>On MELI: I'm parking it, not rejecting it. It generates cash more cheaply than anything else on your list and revenue is growing 50%. But it reported last night and the market hasn't finished digesting it. Worth revisiting in a week once the dust settles.</t>
+          <t>| Compounders | MA | Mastercard | 27 | +17% | 46% | 100% gross margin, ROE 232% — elite |</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Nu Holdings</t>
+          <t>MercadoLibre</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -5994,7 +5986,7 @@
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="9" t="n"/>
       <c r="H99" s="9" t="n">
-        <v>13.84</v>
+        <v>1820.69</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
@@ -6005,23 +5997,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A99)</f>
         <v/>
       </c>
-      <c r="K99" s="5" t="inlineStr"/>
-      <c r="L99" s="5" t="inlineStr"/>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>On MELI: I'm parking it, not rejecting it. It generates cash more cheaply than anything else on your list and revenue is growing 50%. But it reported last night and the market hasn't finished digesting it. Worth revisiting in a week once the dust settles.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Nu Holdings</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -6034,7 +6034,7 @@
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="9" t="n"/>
       <c r="H100" s="9" t="n">
-        <v>59.07</v>
+        <v>13.84</v>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
@@ -6045,31 +6045,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A100)</f>
         <v/>
       </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
+      <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr"/>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>Also pre-existing on the base, not introduced here: four watchlist names (EOSE, TEM, KO, V) now sit outside their own 52-week bands. Those are the same names in the never-merged V/KO/PYPL delta bucket whose prices I already flagged as suspect, so I left them rather than bake a bad price into a widened range.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Sea Limited</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -6082,7 +6074,7 @@
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="9" t="n"/>
       <c r="H101" s="9" t="n">
-        <v>113.43</v>
+        <v>59.07</v>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
@@ -6093,23 +6085,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A101)</f>
         <v/>
       </c>
-      <c r="K101" s="5" t="inlineStr"/>
-      <c r="L101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Also pre-existing on the base, not introduced here: four watchlist names (EOSE, TEM, KO, V) now sit outside their own 52-week bands. Those are the same names in the never-merged V/KO/PYPL delta bucket whose prices I already flagged as suspect, so I left them rather than bake a bad price into a widened range.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -6122,7 +6122,7 @@
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="9" t="n"/>
       <c r="H102" s="9" t="n">
-        <v>151.57</v>
+        <v>113.43</v>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
@@ -6133,31 +6133,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A102)</f>
         <v/>
       </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>SoFi Technologies</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -6170,7 +6162,7 @@
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="9" t="n"/>
       <c r="H103" s="9" t="n">
-        <v>18.38</v>
+        <v>151.57</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -6183,29 +6175,29 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>Worth noting the perverse detail: 12 of the 23 whitelisted names (ADBE, COIN, HOOD, JNJ, KO, PYPL, SBUX, SHOP, SOFI, UBER, UNH, V) are watchlist-only — you own none of them. So nearly half your free entitlement is spent on names you don't hold, while $242K of what you do hold goes unpriced.</t>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>SoundHound AI</t>
+          <t>SoFi Technologies</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -6218,7 +6210,7 @@
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="9" t="n"/>
       <c r="H104" s="9" t="n">
-        <v>8.02</v>
+        <v>18.38</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
@@ -6231,29 +6223,29 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>Worth noting the perverse detail: 12 of the 23 whitelisted names (ADBE, COIN, HOOD, JNJ, KO, PYPL, SBUX, SHOP, SOFI, UBER, UNH, V) are watchlist-only — you own none of them. So nearly half your free entitlement is spent on names you don't hold, while $242K of what you do hold goes unpriced.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Uber Technologies</t>
+          <t>SoundHound AI</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -6266,7 +6258,7 @@
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="9" t="n"/>
       <c r="H105" s="9" t="n">
-        <v>75.02</v>
+        <v>8.02</v>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
@@ -6279,29 +6271,29 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>This is the discipline point. Uber is a sophisticated technology company that deployed AI aggressively across its organisation and, by its own admission, cannot yet prove it paid for itself. "This company uses AI" is not a thesis. "AI attacks a cost line that is large, and compounds on data nobody else has" — that's a thesis.</t>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Uber Technologies</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -6314,7 +6306,7 @@
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="9" t="n"/>
       <c r="H106" s="9" t="n">
-        <v>362.5</v>
+        <v>75.02</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
@@ -6327,52 +6319,42 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
+          <t>This is the discipline point. Uber is a sophisticated technology company that deployed AI aggressively across its organisation and, by its own admission, cannot yet prove it paid for itself. "This company uses AI" is not a thesis. "AI attacks a cost line that is large, and compounds on data nobody else has" — that's a thesis.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F107" s="8" t="n">
-        <v>3914.12</v>
-      </c>
-      <c r="G107" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Fintech / Digital Platform</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="9" t="n"/>
       <c r="H107" s="9" t="n">
-        <v>214.42</v>
+        <v>362.5</v>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
@@ -6385,29 +6367,29 @@
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
+          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -6415,12 +6397,22 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr"/>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="8" t="n"/>
-      <c r="G108" s="9" t="n"/>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>3914.12</v>
+      </c>
+      <c r="G108" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H108" s="9" t="n">
-        <v>159.64</v>
+        <v>214.42</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
@@ -6433,29 +6425,29 @@
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
+          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -6468,7 +6460,7 @@
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="9" t="n"/>
       <c r="H109" s="9" t="n">
-        <v>300.27</v>
+        <v>159.64</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -6491,19 +6483,19 @@
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
+          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -6511,22 +6503,12 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="F110" s="8" t="n">
-        <v>3760.62</v>
-      </c>
-      <c r="G110" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D110" s="11" t="inlineStr"/>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="9" t="n"/>
       <c r="H110" s="9" t="n">
-        <v>363.86</v>
+        <v>300.27</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -6539,29 +6521,29 @@
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -6569,16 +6551,26 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="9" t="n"/>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>3760.62</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H111" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>363.86</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J111" s="5">
@@ -6587,29 +6579,29 @@
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -6622,11 +6614,11 @@
       <c r="F112" s="8" t="n"/>
       <c r="G112" s="9" t="n"/>
       <c r="H112" s="9" t="n">
-        <v>168.68</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J112" s="5">
@@ -6635,52 +6627,42 @@
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F113" s="8" t="n">
-        <v>1994.06</v>
-      </c>
-      <c r="G113" s="9" t="n">
-        <v>5000</v>
-      </c>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr"/>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="8" t="n"/>
+      <c r="G113" s="9" t="n"/>
       <c r="H113" s="9" t="n">
-        <v>169.9</v>
+        <v>168.68</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -6693,29 +6675,29 @@
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Cameco</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -6723,12 +6705,22 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="9" t="n"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>1994.06</v>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>5000</v>
+      </c>
       <c r="H114" s="9" t="n">
-        <v>97.39</v>
+        <v>169.9</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -6741,29 +6733,29 @@
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Cameco</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -6771,22 +6763,12 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F115" s="8" t="n">
-        <v>4040.98</v>
-      </c>
-      <c r="G115" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D115" s="11" t="inlineStr"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="9" t="n"/>
       <c r="H115" s="9" t="n">
-        <v>269.89</v>
+        <v>97.39</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
@@ -6799,29 +6781,29 @@
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -6829,12 +6811,22 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr"/>
-      <c r="E116" s="7" t="n"/>
-      <c r="F116" s="8" t="n"/>
-      <c r="G116" s="9" t="n"/>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F116" s="8" t="n">
+        <v>4040.98</v>
+      </c>
+      <c r="G116" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H116" s="9" t="n">
-        <v>191.37</v>
+        <v>269.89</v>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
@@ -6845,23 +6837,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A116)</f>
         <v/>
       </c>
-      <c r="K116" s="5" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -6874,7 +6874,7 @@
       <c r="F117" s="8" t="n"/>
       <c r="G117" s="9" t="n"/>
       <c r="H117" s="9" t="n">
-        <v>18.85</v>
+        <v>191.37</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -6885,31 +6885,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A117)</f>
         <v/>
       </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L117" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
+      <c r="K117" s="5" t="inlineStr"/>
+      <c r="L117" s="5" t="inlineStr"/>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Oklo</t>
+          <t>Nano Nuclear Energy</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -6922,7 +6914,7 @@
       <c r="F118" s="8" t="n"/>
       <c r="G118" s="9" t="n"/>
       <c r="H118" s="9" t="n">
-        <v>48.42</v>
+        <v>18.85</v>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
@@ -6935,29 +6927,29 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
+          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>NuScale Power</t>
+          <t>Oklo</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -6970,7 +6962,7 @@
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="9" t="n"/>
       <c r="H119" s="9" t="n">
-        <v>9.82</v>
+        <v>48.42</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -6983,29 +6975,29 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
+          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>UUUU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Energy Fuels</t>
+          <t>NuScale Power</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -7018,34 +7010,42 @@
       <c r="F120" s="8" t="n"/>
       <c r="G120" s="9" t="n"/>
       <c r="H120" s="9" t="n">
-        <v>12.9</v>
+        <v>9.82</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J120" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A120)</f>
         <v/>
       </c>
-      <c r="K120" s="5" t="inlineStr"/>
-      <c r="L120" s="5" t="inlineStr"/>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>UUUU</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Energy Fuels</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -7053,57 +7053,39 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F121" s="8" t="n">
-        <v>6078.05</v>
-      </c>
-      <c r="G121" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D121" s="11" t="inlineStr"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="8" t="n"/>
+      <c r="G121" s="9" t="n"/>
       <c r="H121" s="9" t="n">
-        <v>140.67</v>
+        <v>12.9</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J121" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A121)</f>
         <v/>
       </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>X-energy (IPO Apr 24 '26)</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -7111,16 +7093,26 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr"/>
-      <c r="E122" s="7" t="n"/>
-      <c r="F122" s="8" t="n"/>
-      <c r="G122" s="9" t="n"/>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>6078.05</v>
+      </c>
+      <c r="G122" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H122" s="9" t="n">
-        <v>20.82</v>
+        <v>140.67</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J122" s="5">
@@ -7129,56 +7121,46 @@
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>XE</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>X-energy (IPO Apr 24 '26)</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="F123" s="8" t="n">
-        <v>7879.55</v>
-      </c>
-      <c r="G123" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="8" t="n"/>
+      <c r="G123" s="9" t="n"/>
       <c r="H123" s="9" t="n">
-        <v>448.68</v>
+        <v>20.82</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J123" s="5">
@@ -7187,7 +7169,7 @@
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
@@ -7197,19 +7179,19 @@
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7223,16 +7205,16 @@
         </is>
       </c>
       <c r="E124" s="7" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F124" s="8" t="n">
-        <v>2147.3</v>
+        <v>7879.55</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>10000</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>990.3200000000001</v>
+        <v>448.68</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -7245,29 +7227,29 @@
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Hubbell</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -7275,12 +7257,22 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="9" t="n"/>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>2147.3</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H125" s="9" t="n">
-        <v>513.99</v>
+        <v>990.3200000000001</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -7293,29 +7285,29 @@
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Monolithic Power</t>
+          <t>Hubbell</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -7323,22 +7315,12 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>1538.56</v>
-      </c>
-      <c r="G126" s="9" t="n">
-        <v>5000</v>
-      </c>
+      <c r="D126" s="11" t="inlineStr"/>
+      <c r="E126" s="7" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="9" t="n"/>
       <c r="H126" s="9" t="n">
-        <v>1401.54</v>
+        <v>513.99</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -7351,29 +7333,29 @@
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>Monolithic Power</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -7381,12 +7363,22 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr"/>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="8" t="n"/>
-      <c r="G127" s="9" t="n"/>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>1538.56</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>5000</v>
+      </c>
       <c r="H127" s="9" t="n">
-        <v>164.69</v>
+        <v>1401.54</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
@@ -7399,29 +7391,29 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>POWL</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Powell Industries</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -7434,7 +7426,7 @@
       <c r="F128" s="8" t="n"/>
       <c r="G128" s="9" t="n"/>
       <c r="H128" s="9" t="n">
-        <v>211.56</v>
+        <v>164.69</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -7464,12 +7456,12 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Powell Industries</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -7482,7 +7474,7 @@
       <c r="F129" s="8" t="n"/>
       <c r="G129" s="9" t="n"/>
       <c r="H129" s="9" t="n">
-        <v>671.86</v>
+        <v>211.56</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
@@ -7505,24 +7497,24 @@
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>AIRJ</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>AirJoule Technologies</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
+          <t>Power and Electrification</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr"/>
@@ -7530,7 +7522,7 @@
       <c r="F130" s="8" t="n"/>
       <c r="G130" s="9" t="n"/>
       <c r="H130" s="9" t="n">
-        <v>5.92</v>
+        <v>671.86</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -7548,24 +7540,24 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AIRJ</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>AirJoule Technologies</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
@@ -7578,7 +7570,7 @@
       <c r="F131" s="8" t="n"/>
       <c r="G131" s="9" t="n"/>
       <c r="H131" s="9" t="n">
-        <v>219.34</v>
+        <v>5.92</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -7589,23 +7581,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A131)</f>
         <v/>
       </c>
-      <c r="K131" s="5" t="inlineStr"/>
-      <c r="L131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Fluence Energy</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       <c r="F132" s="8" t="n"/>
       <c r="G132" s="9" t="n"/>
       <c r="H132" s="9" t="n">
-        <v>13.2</v>
+        <v>219.34</v>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
@@ -7629,31 +7629,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A132)</f>
         <v/>
       </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
+      <c r="K132" s="5" t="inlineStr"/>
+      <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>MYR Group</t>
+          <t>Fluence Energy</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -7666,7 +7658,7 @@
       <c r="F133" s="8" t="n"/>
       <c r="G133" s="9" t="n"/>
       <c r="H133" s="9" t="n">
-        <v>337.42</v>
+        <v>13.2</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -7677,23 +7669,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A133)</f>
         <v/>
       </c>
-      <c r="K133" s="5" t="inlineStr"/>
-      <c r="L133" s="5" t="inlineStr"/>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>MYR Group</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -7706,7 +7706,7 @@
       <c r="F134" s="8" t="n"/>
       <c r="G134" s="9" t="n"/>
       <c r="H134" s="9" t="n">
-        <v>84.65000000000001</v>
+        <v>337.42</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -7717,31 +7717,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A134)</f>
         <v/>
       </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
@@ -7754,7 +7746,7 @@
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="9" t="n"/>
       <c r="H135" s="9" t="n">
-        <v>118.13</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -7767,29 +7759,29 @@
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Vertiv Holdings</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -7797,22 +7789,12 @@
           <t>Renewal Energy</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F136" s="8" t="n">
-        <v>3524.44</v>
-      </c>
-      <c r="G136" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D136" s="11" t="inlineStr"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="8" t="n"/>
+      <c r="G136" s="9" t="n"/>
       <c r="H136" s="9" t="n">
-        <v>272.4</v>
+        <v>118.13</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -7825,22 +7807,80 @@
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Vertiv Holdings</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Renewal Energy</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F137" s="8" t="n">
+        <v>3524.44</v>
+      </c>
+      <c r="G137" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H137" s="9" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J137" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A137)</f>
+        <v/>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
+      <c r="L137" s="5" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M136" s="10" t="inlineStr">
+      <c r="M137" s="10" t="inlineStr">
         <is>
           <t>Strategically it is also the cleanest fit for what you already own. APH is the interconnect layer — every AI rack you have exposure to through NVDA, AVGO, VRT, ANET and CRDO needs Amphenol's connectors and cable assemblies. It is the pick-and-shovel play on your own book, and it is your smallest deployed position relative to budget.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M136"/>
+  <autoFilter ref="A1:M137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7851,7 +7891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16254,20 +16294,76 @@
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
         <is>
+          <t>STRL</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C194" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  STRL (Sterling Infrastructure) added to Neocloud Watch at the Aug 7 close $547.06. A 'picks-and-shovels' data-centre play - it does the ground/site work UNDER data centres and chip plants. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ High-quality and very profitable: revenue $3.4B, earnings $13.87/share, 40% return on equity, 42% return on capital, strong cash flow, low debt. Record Q2 (+90% revenue) and backlog up 116%.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Its data-centre segment is now ~78% of revenue and grew ~192% - a direct AI-buildout beneficiary. Cheap for the growth (PEG 0.69, forward P/E 25); analysts Strong Buy, avg target ~$919.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Volatile and well off its peak: trades at $547 vs a 52-week high of ~$1,006 (down ~46%), with a $263-$1,006 range. Dipped after Q2 on margin-mix worries before recovering.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
           <t>AFRM</t>
         </is>
       </c>
-      <c r="B194" s="10" t="inlineStr">
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C194" s="12" t="inlineStr">
+      <c r="C195" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D194" s="10" t="inlineStr">
+      <c r="D195" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16289,35 +16385,6 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="10" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B195" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C195" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D195" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- COIN sits with HOOD/AFRM/SHOP as a momentum-and-story name where valuation still has a long way to fall if growth blinks - do not bucket it with V/MA/PYPL quality names.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
         <is>
@@ -16326,15 +16393,44 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- COIN sits with HOOD/AFRM/SHOP as a momentum-and-story name where valuation still has a long way to fall if growth blinks - do not bucket it with V/MA/PYPL quality names.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
           <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
         </is>
       </c>
-      <c r="C196" s="12" t="inlineStr">
+      <c r="C197" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D196" s="10" t="inlineStr">
+      <c r="D197" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16365,23 +16461,23 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="10" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B198" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C197" s="12" t="inlineStr">
+      <c r="C198" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr">
+      <c r="D198" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16403,52 +16499,52 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="B198" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C198" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D198" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Housekeeping error: Fiserv moved to Nasdaq and changed ticker to FISV (announced Oct 29, 2025); the board still shows FI, so its quote may be mismatched - fix due on next push.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Housekeeping error: Fiserv moved to Nasdaq and changed ticker to FISV (announced Oct 29, 2025); the board still shows FI, so its quote may be mismatched - fix due on next push.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B199" s="10" t="inlineStr">
+      <c r="B200" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C199" s="12" t="inlineStr">
+      <c r="C200" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D199" s="10" t="inlineStr">
+      <c r="D200" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16470,35 +16566,6 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="10" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="B200" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C200" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D200" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  HOOD's price was verified against a third outside source to break a tie between conflicting quotes during the data check.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="201">
       <c r="A201" s="10" t="inlineStr">
         <is>
@@ -16507,15 +16574,44 @@
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C201" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  HOOD's price was verified against a third outside source to break a tie between conflicting quotes during the data check.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C201" s="13" t="inlineStr">
+      <c r="C202" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D201" s="10" t="inlineStr">
+      <c r="D202" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16564,23 +16660,23 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>LMND</t>
         </is>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C202" s="14" t="inlineStr">
+      <c r="C203" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D203" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16602,39 +16698,10 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="10" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B203" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C203" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D203" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Mastercard is filed with the elite compounders: 27x earnings, +17% growth, 100% gross margin and a 232% return on equity.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
@@ -16642,9 +16709,9 @@
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C204" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
@@ -16652,10 +16719,10 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Mastercard is filed with the elite compounders: 27x earnings, +17% growth, 100% gross margin and a 232% return on equity.</t>
           </r>
         </is>
       </c>
@@ -16668,15 +16735,44 @@
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C205" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C205" s="13" t="inlineStr">
+      <c r="C206" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D205" s="10" t="inlineStr">
+      <c r="D206" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16707,35 +16803,6 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="B206" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C206" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D206" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Tagged the deep-value pick of the fintech group: cheapest quality name at 10x, off 28% - fits the V/MA toll-road, quality-plus-value wheelhouse.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="207">
       <c r="A207" s="10" t="inlineStr">
         <is>
@@ -16744,15 +16811,44 @@
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C207" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Tagged the deep-value pick of the fintech group: cheapest quality name at 10x, off 28% - fits the V/MA toll-road, quality-plus-value wheelhouse.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
           <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
         </is>
       </c>
-      <c r="C207" s="12" t="inlineStr">
+      <c r="C208" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D207" s="10" t="inlineStr">
+      <c r="D208" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16775,52 +16871,52 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="10" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B208" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C208" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D208" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
         <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C209" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B209" s="10" t="inlineStr">
+      <c r="B210" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C209" s="13" t="inlineStr">
+      <c r="C210" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D209" s="10" t="inlineStr">
+      <c r="D210" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16842,35 +16938,6 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="10" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B210" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C210" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D210" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  SOFI is one of 12 watchlist-only names consuming the free price-feed entitlement while $242K of actually-held stock goes unpriced.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
         <is>
@@ -16879,12 +16946,12 @@
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C211" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C211" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
@@ -16892,10 +16959,10 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Verdict: avoid. Rated Hold at $18.25 with only +9% upside - six firms CUT their targets after a beat, a sign the beat did not matter.</t>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  SOFI is one of 12 watchlist-only names consuming the free price-feed entitlement while $242K of actually-held stock goes unpriced.</t>
           </r>
         </is>
       </c>
@@ -16903,20 +16970,49 @@
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
         <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C212" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Verdict: avoid. Rated Hold at $18.25 with only +9% upside - six firms CUT their targets after a beat, a sign the beat did not matter.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
+        <is>
           <t>SOUN</t>
         </is>
       </c>
-      <c r="B212" s="10" t="inlineStr">
+      <c r="B213" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C212" s="13" t="inlineStr">
+      <c r="C213" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D212" s="10" t="inlineStr">
+      <c r="D213" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16966,35 +17062,6 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B213" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C213" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D213" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
         <is>
@@ -17003,15 +17070,44 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C214" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B215" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C214" s="12" t="inlineStr">
+      <c r="C215" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D214" s="10" t="inlineStr">
+      <c r="D215" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17033,52 +17129,52 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B215" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C215" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D215" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C216" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
           <t>CRWD</t>
         </is>
       </c>
-      <c r="B216" s="10" t="inlineStr">
+      <c r="B217" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C216" s="13" t="inlineStr">
+      <c r="C217" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D216" s="10" t="inlineStr">
+      <c r="D217" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17127,52 +17223,52 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="10" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B217" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C217" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D217" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
         <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="B218" s="10" t="inlineStr">
+      <c r="B219" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C218" s="14" t="inlineStr">
+      <c r="C219" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D218" s="10" t="inlineStr">
+      <c r="D219" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17194,35 +17290,6 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B219" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C219" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D219" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
         <is>
@@ -17231,15 +17298,44 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C220" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C220" s="13" t="inlineStr">
+      <c r="C221" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D220" s="10" t="inlineStr">
+      <c r="D221" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17270,23 +17366,23 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="10" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="B221" s="10" t="inlineStr">
+      <c r="B222" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C221" s="13" t="inlineStr">
+      <c r="C222" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D221" s="10" t="inlineStr">
+      <c r="D222" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17317,52 +17413,52 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="B222" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C222" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D222" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
         <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C223" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
           <t>PANW</t>
         </is>
       </c>
-      <c r="B223" s="10" t="inlineStr">
+      <c r="B224" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C223" s="14" t="inlineStr">
+      <c r="C224" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D223" s="10" t="inlineStr">
+      <c r="D224" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17384,23 +17480,23 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="10" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
         <is>
           <t>RBRK</t>
         </is>
       </c>
-      <c r="B224" s="10" t="inlineStr">
+      <c r="B225" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C224" s="13" t="inlineStr">
+      <c r="C225" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D224" s="10" t="inlineStr">
+      <c r="D225" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17440,23 +17536,23 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="10" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
         <is>
           <t>ZS</t>
         </is>
       </c>
-      <c r="B225" s="10" t="inlineStr">
+      <c r="B226" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C225" s="14" t="inlineStr">
+      <c r="C226" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D225" s="10" t="inlineStr">
+      <c r="D226" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17487,23 +17583,23 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
         <is>
           <t>BWXT</t>
         </is>
       </c>
-      <c r="B226" s="10" t="inlineStr">
+      <c r="B227" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C226" s="13" t="inlineStr">
+      <c r="C227" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D226" s="10" t="inlineStr">
+      <c r="D227" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17534,23 +17630,23 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="10" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
         <is>
           <t>CCJ</t>
         </is>
       </c>
-      <c r="B227" s="10" t="inlineStr">
+      <c r="B228" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C227" s="13" t="inlineStr">
+      <c r="C228" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D227" s="10" t="inlineStr">
+      <c r="D228" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17581,52 +17677,52 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="B228" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C228" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D228" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C229" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
           <t>CEG</t>
         </is>
       </c>
-      <c r="B229" s="10" t="inlineStr">
+      <c r="B230" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C229" s="14" t="inlineStr">
+      <c r="C230" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D229" s="10" t="inlineStr">
+      <c r="D230" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17657,23 +17753,23 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
         <is>
           <t>LEU</t>
         </is>
       </c>
-      <c r="B230" s="10" t="inlineStr">
+      <c r="B231" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C230" s="13" t="inlineStr">
+      <c r="C231" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D230" s="10" t="inlineStr">
+      <c r="D231" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17704,35 +17800,6 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="10" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="B231" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C231" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D231" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
         <is>
@@ -17741,7 +17808,7 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
@@ -17757,7 +17824,7 @@
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
+            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
           </r>
         </is>
       </c>
@@ -17765,20 +17832,49 @@
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
         <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="B233" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B233" s="10" t="inlineStr">
+      <c r="B234" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C233" s="12" t="inlineStr">
+      <c r="C234" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D233" s="10" t="inlineStr">
+      <c r="D234" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17809,52 +17905,52 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="B234" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C234" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D234" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="235">
       <c r="A235" s="10" t="inlineStr">
         <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C235" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
           <t>SMR</t>
         </is>
       </c>
-      <c r="B235" s="10" t="inlineStr">
+      <c r="B236" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C235" s="12" t="inlineStr">
+      <c r="C236" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D235" s="10" t="inlineStr">
+      <c r="D236" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17885,23 +17981,23 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="10" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
         <is>
           <t>UUUU</t>
         </is>
       </c>
-      <c r="B236" s="10" t="inlineStr">
+      <c r="B237" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C236" s="13" t="inlineStr">
+      <c r="C237" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D236" s="10" t="inlineStr">
+      <c r="D237" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17932,35 +18028,6 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B237" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C237" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D237" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="238">
       <c r="A238" s="10" t="inlineStr">
         <is>
@@ -17969,15 +18036,44 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C238" s="12" t="inlineStr">
+      <c r="C239" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D238" s="10" t="inlineStr">
+      <c r="D239" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18017,23 +18113,23 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
         <is>
           <t>XE</t>
         </is>
       </c>
-      <c r="B239" s="10" t="inlineStr">
+      <c r="B240" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C239" s="13" t="inlineStr">
+      <c r="C240" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D239" s="10" t="inlineStr">
+      <c r="D240" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18055,35 +18151,6 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B240" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C240" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D240" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
         <is>
@@ -18092,15 +18159,44 @@
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C241" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
           <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
         </is>
       </c>
-      <c r="C241" s="12" t="inlineStr">
+      <c r="C242" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D241" s="10" t="inlineStr">
+      <c r="D242" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18122,44 +18218,15 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B242" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C242" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D242" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
       <c r="C243" s="13" t="inlineStr">
@@ -18175,7 +18242,7 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
+            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
           </r>
         </is>
       </c>
@@ -18188,15 +18255,44 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C244" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B245" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C244" s="12" t="inlineStr">
+      <c r="C245" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D244" s="10" t="inlineStr">
+      <c r="D245" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18218,23 +18314,23 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
         <is>
           <t>HUBB</t>
         </is>
       </c>
-      <c r="B245" s="10" t="inlineStr">
+      <c r="B246" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C245" s="14" t="inlineStr">
+      <c r="C246" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D245" s="10" t="inlineStr">
+      <c r="D246" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18265,35 +18361,6 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C246" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
         <is>
@@ -18302,15 +18369,44 @@
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C247" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
           <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
         </is>
       </c>
-      <c r="C247" s="12" t="inlineStr">
+      <c r="C248" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D247" s="10" t="inlineStr">
+      <c r="D248" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18342,23 +18438,23 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="10" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
         <is>
           <t>MPWR</t>
         </is>
       </c>
-      <c r="B248" s="10" t="inlineStr">
+      <c r="B249" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C248" s="13" t="inlineStr">
+      <c r="C249" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D248" s="10" t="inlineStr">
+      <c r="D249" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18389,23 +18485,23 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="10" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
         <is>
           <t>NVT</t>
         </is>
       </c>
-      <c r="B249" s="10" t="inlineStr">
+      <c r="B250" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C249" s="14" t="inlineStr">
+      <c r="C250" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D249" s="10" t="inlineStr">
+      <c r="D250" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18436,23 +18532,23 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="10" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
         <is>
           <t>POWL</t>
         </is>
       </c>
-      <c r="B250" s="10" t="inlineStr">
+      <c r="B251" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C250" s="13" t="inlineStr">
+      <c r="C251" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D250" s="10" t="inlineStr">
+      <c r="D251" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18483,23 +18579,23 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="10" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
         <is>
           <t>PWR</t>
         </is>
       </c>
-      <c r="B251" s="10" t="inlineStr">
+      <c r="B252" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C251" s="14" t="inlineStr">
+      <c r="C252" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D251" s="10" t="inlineStr">
+      <c r="D252" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18521,23 +18617,23 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="10" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
         <is>
           <t>AIRJ</t>
         </is>
       </c>
-      <c r="B252" s="10" t="inlineStr">
+      <c r="B253" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C252" s="13" t="inlineStr">
+      <c r="C253" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D252" s="10" t="inlineStr">
+      <c r="D253" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18604,52 +18700,52 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="B253" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C253" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="254">
       <c r="A254" s="10" t="inlineStr">
         <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C254" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="inlineStr">
+        <is>
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B254" s="10" t="inlineStr">
+      <c r="B255" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C254" s="12" t="inlineStr">
+      <c r="C255" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D254" s="10" t="inlineStr">
+      <c r="D255" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18699,23 +18795,23 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="10" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
         <is>
           <t>MYRG</t>
         </is>
       </c>
-      <c r="B255" s="10" t="inlineStr">
+      <c r="B256" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C255" s="13" t="inlineStr">
+      <c r="C256" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D255" s="10" t="inlineStr">
+      <c r="D256" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18755,23 +18851,23 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="10" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
         <is>
           <t>NEE</t>
         </is>
       </c>
-      <c r="B256" s="10" t="inlineStr">
+      <c r="B257" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C256" s="14" t="inlineStr">
+      <c r="C257" s="14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
       </c>
-      <c r="D256" s="10" t="inlineStr">
+      <c r="D257" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18793,23 +18889,23 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="10" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
         <is>
           <t>NEE</t>
         </is>
       </c>
-      <c r="B257" s="10" t="inlineStr">
+      <c r="B258" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C257" s="13" t="inlineStr">
+      <c r="C258" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D257" s="10" t="inlineStr">
+      <c r="D258" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18831,23 +18927,23 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="10" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
         <is>
           <t>NRG</t>
         </is>
       </c>
-      <c r="B258" s="10" t="inlineStr">
+      <c r="B259" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C258" s="13" t="inlineStr">
+      <c r="C259" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D258" s="10" t="inlineStr">
+      <c r="D259" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18914,23 +19010,23 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="10" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
         <is>
           <t>VRT</t>
         </is>
       </c>
-      <c r="B259" s="10" t="inlineStr">
+      <c r="B260" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C259" s="12" t="inlineStr">
+      <c r="C260" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D259" s="10" t="inlineStr">
+      <c r="D260" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18952,35 +19048,6 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B260" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C260" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D260" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
-          </r>
-        </is>
-      </c>
-    </row>
     <row r="261">
       <c r="A261" s="10" t="inlineStr">
         <is>
@@ -18989,15 +19056,44 @@
       </c>
       <c r="B261" s="10" t="inlineStr">
         <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C261" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C261" s="13" t="inlineStr">
+      <c r="C262" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D261" s="10" t="inlineStr">
+      <c r="D262" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19020,7 +19116,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D261"/>
+  <autoFilter ref="A1:D262"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51440,7 +51536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -52213,8 +52309,25 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>83323da</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Aug 7-8 batch. NUCLEAR ENERGY (g16): XE (X-energy, an SMR/nuclear-reactor developer) MOVED from Energy -&gt; Nuclear Energy (watchlist, no position - it was always a nuclear name so this is its proper home). Added UUUU (Energy Fuels, NYSE American) at the Aug 6 close 12.90 - a US URANIUM miner + rare-earth processor (White Mesa Mill, Utah); Aug 7 rebounded +9.61% to 14.14. It is NOT profitable: revenue only 105.76M TTM, net margin -77%, EPS -0.34, free cash flow -120M, so P/E, forward P/E, PEG, P/FCF, EV/EBITDA all n/a; but the balance sheet is strong (working capital ~996M: cash 58.4M + marketable securities 878.3M). Q2 (Aug 5) revenue 25.1M, net loss 33.4M; 865k lbs U3O8 produced, sold at 80.48/lb; building a Heavy Rare-Earth plant. SHORT INTEREST 19.74%. ath 27.90 = 52-wk high proxy (true ATH NOT FOUND). Added LEU (Centrus Energy, NYSE American) at the Aug 7 close 191.37 (Aug 6 close was 178.03, DOWN 5.12% on earnings, then Aug 7 REBOUNDED +7.49%; stored at the Aug-7-consistent stats). Centrus is the only US-owned uranium ENRICHER, making HALEU fuel for advanced/SMR reactors. Profitable on a GAAP basis: revenue 473.9M TTM, net margin 10.23%, EPS 2.17, but trailing P/E is a rich 88 and EV/EBITDA 179.64 (a chart-scale outlier like AXTI/AXON), free cash flow NEGATIVE -164M on heavy enrichment-capacity capex. Backlog 4.5B through 2040; signed a 900M DOE HALEU award and first commercial HALEU supply deal; cash 1.87B. SHORT INTEREST 26.03% (very high). ath 464.25 = 52-wk high proxy; note 52-wk low 142.13 - this stock swings violently. For BOTH UUUU and LEU: jan2, revG (TTM), epsG NOT FOUND; analyst sets conflict (UUUU stockanalysis 7 analysts avg 26.13 vs MarketBeat 4 avg 23.25; LEU stockanalysis 17 avg 260.87 vs MarketBeat 13 avg 246.17) - stockanalysis taken. NEW GROUP 'Renewal Energy' (g18, colour slot --s19 added to both themes): MOVED VRT, NEE, BE, AIRJ, FLNC and NRG out of Energy into it (all watchlist except none held here; field values/positions untouched, group P&amp;L re-attributed), and ADDED MYRG. NOTE the user wrote the label 'Renewal Energy' and the ticker '$ MYR'; the label was kept verbatim (most likely intended 'Renewable Energy' - offered to rename) and MYR resolves to MYR Group Inc which trades as MYRG, so it was added under MYRG. MYRG added at the Aug 7 close 337.42 - a high-quality ELECTRICAL-INFRASTRUCTURE contractor (transmission &amp; distribution for utilities + commercial/industrial electrical incl. data centres and grid buildout). Genuinely profitable and compounding: revenue 4.01B TTM (+16.1%), EPS 10.54 (+121%), ROE 24.71%, ROIC 25.59%, positive free cash flow 193M, low debt (D/E 0.09), P/E 32 / forward 26. Record Q2 (Jul 29): revenue 1.08B beat ~995M, EPS 3.17 beat 2.64, record backlog 3.16B; acquired Valley Electric + Comet Electric (closed Jul 1). ath 503.57 = 52-wk high proxy (intraday Jun 30 2026; close that day 500.40); jan2 NOT FOUND. After these moves Energy (g5) retains TE, EOSE, ENPH, AMPX. Group counts: Nuclear Energy 7 -&gt; 10, Energy 11 -&gt; 4, Renewal Energy new = 7.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C45"/>
+  <autoFilter ref="A1:C46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Pillar4_Stock_Notes.xlsx
+++ b/Pillar4_Stock_Notes.xlsx
@@ -17,9 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Index'!$A$1:$M$147</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$272</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$274</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Full Log'!$A$1:$D$1473</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Our Notes'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Follow-ups'!$A$1:$D$20</definedName>
   </definedNames>
@@ -6016,12 +6016,12 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Affirm Holdings</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -6034,11 +6034,11 @@
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="9" t="n"/>
       <c r="H101" s="9" t="n">
-        <v>79.56</v>
+        <v>152.89</v>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J101" s="5">
@@ -6052,24 +6052,24 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>The dangerous category — and this is the one worth knowing about. StockTwits, CNN Business, Simply Wall St and TradingView all hand me a price with no date attached to it. That is far more dangerous than a site that fails, because a wrong number that looks confident is indistinguishable from a right one. I have a rule now: no date stamp, no use. TradingKey deserves special mention — it has correct dates but its percentage moves are simply wrong (it showed COIN at −8.03% when the real move was −10.59%), so you can't work backwards from it either.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -6082,7 +6082,7 @@
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="9" t="n"/>
       <c r="H102" s="9" t="n">
-        <v>152.89</v>
+        <v>52.41</v>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
@@ -6100,24 +6100,24 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>The dangerous category — and this is the one worth knowing about. StockTwits, CNN Business, Simply Wall St and TradingView all hand me a price with no date attached to it. That is far more dangerous than a site that fails, because a wrong number that looks confident is indistinguishable from a right one. I have a rule now: no date stamp, no use. TradingKey deserves special mention — it has correct dates but its percentage moves are simply wrong (it showed COIN at −8.03% when the real move was −10.59%), so you can't work backwards from it either.</t>
+          <t>⚠️ Two things, and the first is a housekeeping error on our side: the ticker is no longer FI. Fiserv moved to Nasdaq and changed to FISV (announced October 29, 2025). Our board still carries it as FI, which means the quote we've been showing may not be reliably matched. I'll correct that on the next push.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Robinhood Markets</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -6130,7 +6130,7 @@
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="9" t="n"/>
       <c r="H103" s="9" t="n">
-        <v>52.41</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -6143,29 +6143,29 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Two things, and the first is a housekeeping error on our side: the ticker is no longer FI. Fiserv moved to Nasdaq and changed to FISV (announced October 29, 2025). Our board still carries it as FI, which means the quote we've been showing may not be reliably matched. I'll correct that on the next push.</t>
+          <t>The honest bear case: Robinhood trades at 16.5× its revenue against a historical average of 11.9×. If it simply drifts back to its own normal valuation, that's 30%+ downside with nothing else going wrong. And its earnings depend on retail investors trading actively — in a dull market, that dries up fast.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Robinhood Markets</t>
+          <t>Lemonade</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -6178,11 +6178,11 @@
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="9" t="n"/>
       <c r="H104" s="9" t="n">
-        <v>93.29000000000001</v>
+        <v>51.86</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J104" s="5">
@@ -6191,29 +6191,29 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>The honest bear case: Robinhood trades at 16.5× its revenue against a historical average of 11.9×. If it simply drifts back to its own normal valuation, that's 30%+ downside with nothing else going wrong. And its earnings depend on retail investors trading actively — in a dull market, that dries up fast.</t>
+          <t>One number I couldn't double-check. AIRJ's $5.84 close comes from a single source. The usual quote page was serving a mid-afternoon snapshot rather than the closing price, and no other free source had Aug 4 data for it. Everything else is corroborated — Lemonade's $54.11 was confirmed by two independent sources after the first two disagreed, and Hinge's $79.42 was confirmed by a news article quoting the same figure.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Lemonade</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -6226,11 +6226,11 @@
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="9" t="n"/>
       <c r="H105" s="9" t="n">
-        <v>51.86</v>
+        <v>562.95</v>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J105" s="5">
@@ -6239,29 +6239,29 @@
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>One number I couldn't double-check. AIRJ's $5.84 close comes from a single source. The usual quote page was serving a mid-afternoon snapshot rather than the closing price, and no other free source had Aug 4 data for it. Everything else is corroborated — Lemonade's $54.11 was confirmed by two independent sources after the first two disagreed, and Hinge's $79.42 was confirmed by a news article quoting the same figure.</t>
+          <t>| Compounders | MA | Mastercard | 27 | +17% | 46% | 100% gross margin, ROE 232% — elite |</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Nu Holdings</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -6274,7 +6274,7 @@
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="9" t="n"/>
       <c r="H106" s="9" t="n">
-        <v>562.95</v>
+        <v>13.84</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
@@ -6285,31 +6285,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A106)</f>
         <v/>
       </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K106" s="5" t="inlineStr"/>
+      <c r="L106" s="5" t="inlineStr"/>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>| Compounders | MA | Mastercard | 27 | +17% | 46% | 100% gross margin, ROE 232% — elite |</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>MercadoLibre</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -6322,7 +6314,7 @@
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="9" t="n"/>
       <c r="H107" s="9" t="n">
-        <v>1820.69</v>
+        <v>59.07</v>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
@@ -6335,29 +6327,29 @@
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>On MELI: I'm parking it, not rejecting it. It generates cash more cheaply than anything else on your list and revenue is growing 50%. But it reported last night and the market hasn't finished digesting it. Worth revisiting in a week once the dust settles.</t>
+          <t>Also pre-existing on the base, not introduced here: four watchlist names (EOSE, TEM, KO, V) now sit outside their own 52-week bands. Those are the same names in the never-merged V/KO/PYPL delta bucket whose prices I already flagged as suspect, so I left them rather than bake a bad price into a widened range.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Nu Holdings</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -6370,7 +6362,7 @@
       <c r="F108" s="8" t="n"/>
       <c r="G108" s="9" t="n"/>
       <c r="H108" s="9" t="n">
-        <v>13.84</v>
+        <v>113.43</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
@@ -6392,12 +6384,12 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>SoFi Technologies</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -6410,7 +6402,7 @@
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="9" t="n"/>
       <c r="H109" s="9" t="n">
-        <v>59.07</v>
+        <v>18.38</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -6423,29 +6415,29 @@
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>Also pre-existing on the base, not introduced here: four watchlist names (EOSE, TEM, KO, V) now sit outside their own 52-week bands. Those are the same names in the never-merged V/KO/PYPL delta bucket whose prices I already flagged as suspect, so I left them rather than bake a bad price into a widened range.</t>
+          <t>Worth noting the perverse detail: 12 of the 23 whitelisted names (ADBE, COIN, HOOD, JNJ, KO, PYPL, SBUX, SHOP, SOFI, UBER, UNH, V) are watchlist-only — you own none of them. So nearly half your free entitlement is spent on names you don't hold, while $242K of what you do hold goes unpriced.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Sea Limited</t>
+          <t>SoundHound AI</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -6458,7 +6450,7 @@
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="9" t="n"/>
       <c r="H110" s="9" t="n">
-        <v>113.43</v>
+        <v>8.02</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -6469,23 +6461,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A110)</f>
         <v/>
       </c>
-      <c r="K110" s="5" t="inlineStr"/>
-      <c r="L110" s="5" t="inlineStr"/>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -6498,7 +6498,7 @@
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="9" t="n"/>
       <c r="H111" s="9" t="n">
-        <v>151.57</v>
+        <v>362.5</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
@@ -6521,32 +6521,42 @@
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>SoFi Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
-        </is>
-      </c>
-      <c r="D112" s="11" t="inlineStr"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8" t="n"/>
-      <c r="G112" s="9" t="n"/>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>3914.12</v>
+      </c>
+      <c r="G112" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H112" s="9" t="n">
-        <v>18.38</v>
+        <v>214.42</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
@@ -6559,34 +6569,34 @@
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>Worth noting the perverse detail: 12 of the 23 whitelisted names (ADBE, COIN, HOOD, JNJ, KO, PYPL, SBUX, SHOP, SOFI, UBER, UNH, V) are watchlist-only — you own none of them. So nearly half your free entitlement is spent on names you don't hold, while $242K of what you do hold goes unpriced.</t>
+          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>SoundHound AI</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr"/>
@@ -6594,7 +6604,7 @@
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="9" t="n"/>
       <c r="H113" s="9" t="n">
-        <v>8.02</v>
+        <v>159.64</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -6607,34 +6617,34 @@
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Uber Technologies</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr"/>
@@ -6642,7 +6652,7 @@
       <c r="F114" s="8" t="n"/>
       <c r="G114" s="9" t="n"/>
       <c r="H114" s="9" t="n">
-        <v>75.02</v>
+        <v>300.27</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -6655,42 +6665,52 @@
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>This is the discipline point. Uber is a sophisticated technology company that deployed AI aggressively across its organisation and, by its own admission, cannot yet prove it paid for itself. "This company uses AI" is not a thesis. "AI attacks a cost line that is large, and compounds on data nobody else has" — that's a thesis.</t>
+          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
-        </is>
-      </c>
-      <c r="D115" s="11" t="inlineStr"/>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="8" t="n"/>
-      <c r="G115" s="9" t="n"/>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>3760.62</v>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H115" s="9" t="n">
-        <v>362.5</v>
+        <v>363.86</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
@@ -6703,29 +6723,29 @@
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -6733,26 +6753,16 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F116" s="8" t="n">
-        <v>3914.12</v>
-      </c>
-      <c r="G116" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D116" s="11" t="inlineStr"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="8" t="n"/>
+      <c r="G116" s="9" t="n"/>
       <c r="H116" s="9" t="n">
-        <v>214.42</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J116" s="5">
@@ -6761,29 +6771,29 @@
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -6796,7 +6806,7 @@
       <c r="F117" s="8" t="n"/>
       <c r="G117" s="9" t="n"/>
       <c r="H117" s="9" t="n">
-        <v>159.64</v>
+        <v>168.68</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -6814,37 +6824,47 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="8" t="n"/>
-      <c r="G118" s="9" t="n"/>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>1994.06</v>
+      </c>
+      <c r="G118" s="9" t="n">
+        <v>5000</v>
+      </c>
       <c r="H118" s="9" t="n">
-        <v>300.27</v>
+        <v>169.9</v>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
@@ -6857,52 +6877,42 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
+          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Cameco</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="F119" s="8" t="n">
-        <v>3760.62</v>
-      </c>
-      <c r="G119" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="8" t="n"/>
+      <c r="G119" s="9" t="n"/>
       <c r="H119" s="9" t="n">
-        <v>363.86</v>
+        <v>97.39</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -6915,46 +6925,56 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr"/>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="8" t="n"/>
-      <c r="G120" s="9" t="n"/>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>4040.98</v>
+      </c>
+      <c r="G120" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H120" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>269.89</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J120" s="5">
@@ -6968,29 +6988,29 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Nuclear Energy</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr"/>
@@ -6998,7 +7018,7 @@
       <c r="F121" s="8" t="n"/>
       <c r="G121" s="9" t="n"/>
       <c r="H121" s="9" t="n">
-        <v>168.68</v>
+        <v>191.37</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
@@ -7009,31 +7029,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A121)</f>
         <v/>
       </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+      <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Nano Nuclear Energy</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -7041,22 +7053,12 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F122" s="8" t="n">
-        <v>1994.06</v>
-      </c>
-      <c r="G122" s="9" t="n">
-        <v>5000</v>
-      </c>
+      <c r="D122" s="11" t="inlineStr"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="8" t="n"/>
+      <c r="G122" s="9" t="n"/>
       <c r="H122" s="9" t="n">
-        <v>169.9</v>
+        <v>18.85</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -7069,29 +7071,29 @@
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
+          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Cameco</t>
+          <t>Oklo</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -7104,7 +7106,7 @@
       <c r="F123" s="8" t="n"/>
       <c r="G123" s="9" t="n"/>
       <c r="H123" s="9" t="n">
-        <v>97.39</v>
+        <v>48.42</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
@@ -7117,29 +7119,29 @@
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>NuScale Power</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7147,22 +7149,12 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F124" s="8" t="n">
-        <v>4040.98</v>
-      </c>
-      <c r="G124" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D124" s="11" t="inlineStr"/>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="8" t="n"/>
+      <c r="G124" s="9" t="n"/>
       <c r="H124" s="9" t="n">
-        <v>269.89</v>
+        <v>9.82</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -7175,29 +7167,29 @@
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>UUUU</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>Energy Fuels</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -7210,11 +7202,11 @@
       <c r="F125" s="8" t="n"/>
       <c r="G125" s="9" t="n"/>
       <c r="H125" s="9" t="n">
-        <v>191.37</v>
+        <v>12.9</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J125" s="5">
@@ -7232,12 +7224,12 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -7245,12 +7237,22 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr"/>
-      <c r="E126" s="7" t="n"/>
-      <c r="F126" s="8" t="n"/>
-      <c r="G126" s="9" t="n"/>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>6078.05</v>
+      </c>
+      <c r="G126" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H126" s="9" t="n">
-        <v>18.85</v>
+        <v>140.67</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -7263,29 +7265,29 @@
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>XE</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Oklo</t>
+          <t>X-energy (IPO Apr 24 '26)</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
@@ -7298,11 +7300,11 @@
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="9" t="n"/>
       <c r="H127" s="9" t="n">
-        <v>48.42</v>
+        <v>20.82</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J127" s="5">
@@ -7311,42 +7313,52 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
+          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>NuScale Power</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr"/>
-      <c r="E128" s="7" t="n"/>
-      <c r="F128" s="8" t="n"/>
-      <c r="G128" s="9" t="n"/>
+          <t>Power and Electrification</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F128" s="8" t="n">
+        <v>7879.55</v>
+      </c>
+      <c r="G128" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H128" s="9" t="n">
-        <v>9.82</v>
+        <v>448.68</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -7359,92 +7371,100 @@
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>UUUU</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Energy Fuels</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr"/>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="8" t="n"/>
-      <c r="G129" s="9" t="n"/>
+          <t>Power and Electrification</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>2147.3</v>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H129" s="9" t="n">
-        <v>12.9</v>
+        <v>990.3200000000001</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J129" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A129)</f>
         <v/>
       </c>
-      <c r="K129" s="5" t="inlineStr"/>
-      <c r="L129" s="5" t="inlineStr"/>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>Hubbell</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F130" s="8" t="n">
-        <v>6078.05</v>
-      </c>
-      <c r="G130" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Power and Electrification</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr"/>
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="8" t="n"/>
+      <c r="G130" s="9" t="n"/>
       <c r="H130" s="9" t="n">
-        <v>140.67</v>
+        <v>513.99</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -7457,34 +7477,34 @@
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>HYLN</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>X-energy (IPO Apr 24 '26)</t>
+          <t>Hyliion Holdings</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
+          <t>Power and Electrification</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr"/>
@@ -7492,42 +7512,34 @@
       <c r="F131" s="8" t="n"/>
       <c r="G131" s="9" t="n"/>
       <c r="H131" s="9" t="n">
-        <v>20.82</v>
+        <v>3.87</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J131" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A131)</f>
         <v/>
       </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Monolithic Power</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -7541,16 +7553,16 @@
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>7879.55</v>
+        <v>1538.56</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>448.68</v>
+        <v>1401.54</v>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
@@ -7563,29 +7575,29 @@
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -7593,22 +7605,12 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F133" s="8" t="n">
-        <v>2147.3</v>
-      </c>
-      <c r="G133" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D133" s="11" t="inlineStr"/>
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="8" t="n"/>
+      <c r="G133" s="9" t="n"/>
       <c r="H133" s="9" t="n">
-        <v>990.3200000000001</v>
+        <v>164.69</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -7621,29 +7623,29 @@
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>POWI</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Hubbell</t>
+          <t>Power Integrations</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -7656,7 +7658,7 @@
       <c r="F134" s="8" t="n"/>
       <c r="G134" s="9" t="n"/>
       <c r="H134" s="9" t="n">
-        <v>513.99</v>
+        <v>64.59</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -7667,31 +7669,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A134)</f>
         <v/>
       </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>HYLN</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Hyliion Holdings</t>
+          <t>Powell Industries</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
@@ -7704,7 +7698,7 @@
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="9" t="n"/>
       <c r="H135" s="9" t="n">
-        <v>3.87</v>
+        <v>211.56</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -7715,23 +7709,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A135)</f>
         <v/>
       </c>
-      <c r="K135" s="5" t="inlineStr"/>
-      <c r="L135" s="5" t="inlineStr"/>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Monolithic Power</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -7739,22 +7741,12 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" s="8" t="n">
-        <v>1538.56</v>
-      </c>
-      <c r="G136" s="9" t="n">
-        <v>5000</v>
-      </c>
+      <c r="D136" s="11" t="inlineStr"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="8" t="n"/>
+      <c r="G136" s="9" t="n"/>
       <c r="H136" s="9" t="n">
-        <v>1401.54</v>
+        <v>671.86</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -7767,34 +7759,34 @@
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>AIRJ</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>AirJoule Technologies</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
+          <t>Renewal Energy</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr"/>
@@ -7802,7 +7794,7 @@
       <c r="F137" s="8" t="n"/>
       <c r="G137" s="9" t="n"/>
       <c r="H137" s="9" t="n">
-        <v>164.69</v>
+        <v>5.92</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -7820,29 +7812,29 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>POWI</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Power Integrations</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
+          <t>Renewal Energy</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr"/>
@@ -7850,7 +7842,7 @@
       <c r="F138" s="8" t="n"/>
       <c r="G138" s="9" t="n"/>
       <c r="H138" s="9" t="n">
-        <v>64.59</v>
+        <v>219.34</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -7872,17 +7864,17 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>POWL</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Powell Industries</t>
+          <t>Fluence Energy</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
+          <t>Renewal Energy</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr"/>
@@ -7890,7 +7882,7 @@
       <c r="F139" s="8" t="n"/>
       <c r="G139" s="9" t="n"/>
       <c r="H139" s="9" t="n">
-        <v>211.56</v>
+        <v>13.2</v>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
@@ -7903,34 +7895,34 @@
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>MYR Group</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
+          <t>Renewal Energy</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr"/>
@@ -7938,7 +7930,7 @@
       <c r="F140" s="8" t="n"/>
       <c r="G140" s="9" t="n"/>
       <c r="H140" s="9" t="n">
-        <v>671.86</v>
+        <v>337.42</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -7949,31 +7941,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A140)</f>
         <v/>
       </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr"/>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>AIRJ</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>AirJoule Technologies</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -7986,7 +7970,7 @@
       <c r="F141" s="8" t="n"/>
       <c r="G141" s="9" t="n"/>
       <c r="H141" s="9" t="n">
-        <v>5.92</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -7999,29 +7983,29 @@
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -8034,7 +8018,7 @@
       <c r="F142" s="8" t="n"/>
       <c r="G142" s="9" t="n"/>
       <c r="H142" s="9" t="n">
-        <v>219.34</v>
+        <v>118.13</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -8045,23 +8029,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A142)</f>
         <v/>
       </c>
-      <c r="K142" s="5" t="inlineStr"/>
-      <c r="L142" s="5" t="inlineStr"/>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Fluence Energy</t>
+          <t>Vertiv Holdings</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
@@ -8069,12 +8061,22 @@
           <t>Renewal Energy</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr"/>
-      <c r="E143" s="7" t="n"/>
-      <c r="F143" s="8" t="n"/>
-      <c r="G143" s="9" t="n"/>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F143" s="8" t="n">
+        <v>3524.44</v>
+      </c>
+      <c r="G143" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H143" s="9" t="n">
-        <v>13.2</v>
+        <v>272.4</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -8087,34 +8089,34 @@
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
-          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
+          <t>Strategically it is also the cleanest fit for what you already own. APH is the interconnect layer — every AI rack you have exposure to through NVDA, AVGO, VRT, ANET and CRDO needs Amphenol's connectors and cable assemblies. It is the pick-and-shovel play on your own book, and it is your smallest deployed position relative to budget.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>MYR Group</t>
+          <t>Affirm Holdings</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
+          <t>Digital Applications</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr"/>
@@ -8122,39 +8124,47 @@
       <c r="F144" s="8" t="n"/>
       <c r="G144" s="9" t="n"/>
       <c r="H144" s="9" t="n">
-        <v>337.42</v>
+        <v>79.56</v>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="J144" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A144)</f>
         <v/>
       </c>
-      <c r="K144" s="5" t="inlineStr"/>
-      <c r="L144" s="5" t="inlineStr"/>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>MercadoLibre</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
+          <t>Digital Applications</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr"/>
@@ -8162,7 +8172,7 @@
       <c r="F145" s="8" t="n"/>
       <c r="G145" s="9" t="n"/>
       <c r="H145" s="9" t="n">
-        <v>84.65000000000001</v>
+        <v>1820.69</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -8175,34 +8185,34 @@
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>On MELI: I'm parking it, not rejecting it. It generates cash more cheaply than anything else on your list and revenue is growing 50%. But it reported last night and the market hasn't finished digesting it. Worth revisiting in a week once the dust settles.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
+          <t>Digital Applications</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr"/>
@@ -8210,7 +8220,7 @@
       <c r="F146" s="8" t="n"/>
       <c r="G146" s="9" t="n"/>
       <c r="H146" s="9" t="n">
-        <v>118.13</v>
+        <v>151.57</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -8223,52 +8233,42 @@
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Vertiv Holdings</t>
+          <t>Uber Technologies</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F147" s="8" t="n">
-        <v>3524.44</v>
-      </c>
-      <c r="G147" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Digital Applications</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr"/>
+      <c r="E147" s="7" t="n"/>
+      <c r="F147" s="8" t="n"/>
+      <c r="G147" s="9" t="n"/>
       <c r="H147" s="9" t="n">
-        <v>272.4</v>
+        <v>75.02</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
-          <t>Strategically it is also the cleanest fit for what you already own. APH is the interconnect layer — every AI rack you have exposure to through NVDA, AVGO, VRT, ANET and CRDO needs Amphenol's connectors and cable assemblies. It is the pick-and-shovel play on your own book, and it is your smallest deployed position relative to budget.</t>
+          <t>This is the discipline point. Uber is a sophisticated technology company that deployed AI aggressively across its organisation and, by its own admission, cannot yet prove it paid for itself. "This company uses AI" is not a thesis. "AI attacks a cost line that is large, and compounds on data nobody else has" — that's a thesis.</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17189,20 +17189,2673 @@
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
         <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- COIN sits with HOOD/AFRM/SHOP as a momentum-and-story name where valuation still has a long way to fall if growth blinks - do not bucket it with V/MA/PYPL quality names.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Q2 brought a third straight quarterly loss; the stock dropped 13.4% and TTM earnings turned negative, nulling P/E, forward P/E, PEG, EV/EBITDA and Rule-of-40.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Dad's item #8 was read as COIN with a $300 limit vs a $164 price - inconsistent with his other limits (7-39% below market); likely a typo or misread, needs confirming.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: the official Jul 31 close was $146.26 (-10.59%); several sources showed undated or wrong figures (one said -8.03%), so prices were verified via post-close articles.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Fiserv is the hardest flag in the fintech group: down 71% from its high at 6x forward - a potential value trap, not a bargain; growth decelerating with guidance cuts.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Advisor recommends a deep-dive to settle the value-trap question before anyone acts on the low multiple.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D206" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Housekeeping error: Fiserv moved to Nasdaq and changed ticker to FISV (announced Oct 29, 2025); the board still shows FI, so its quote may be mismatched - fix due on next push.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C207" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  HOOD appears among the pre-dashboard closed trades (with TTD, MELI, APP, SOFI) captured in the new 'Closed / other' line of the group summary.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Framing: HOOD sits with COIN, AFRM and SHOP as momentum-and-story names where valuation still has a long way to fall if growth blinks — not with the V/MA/PYPL quality bucket.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C208" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  HOOD's price was verified against a third outside source to break a tie between conflicting quotes during the data check.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C209" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ HOOD beat on July 29: revenue $1.31B (+32%) and EPS $0.62 vs $0.43 expected (a 44% beat), with almost no debt; it bottomed at $63.52 in March and has recovered 45% since.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ All 26 analyst targets sit above the $92.80 price (+32% implied upside); even the lowest target on the desk is $100 — you are not fighting the crowd.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  The 40% drawdown is read as cyclical, not structural: crypto trading revenue fell 38% with Bitcoin and Ethereum off their peaks and comes back when crypto recovers.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Bear case: HOOD trades at 16.5x revenue vs its 11.9x historical average — 30%+ downside if it merely reverts — and earnings depend on retail traders staying active.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Conviction Medium, 6-24 month horizon; the thesis breaks if monthly funded customers fall for two straight quarters.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="inlineStr">
+        <is>
+          <t>LMND</t>
+        </is>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D210" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Lemonade's report showed its loss ratio improving from 78% to 62% with fewer staff; rated 4 of 5 with +27% to target - but small, volatile and still loss-making.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Flagged as one of two genuinely new AI-beneficiary ideas (small, speculative); added to Fintech/Digital Platform at $54.11 after two independent sources confirmed the price.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B211" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C211" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D211" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Mastercard is filed with the elite compounders: 27x earnings, +17% growth, 100% gross margin and a 232% return on equity.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C212" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Tagged the deep-value pick of the fintech group: cheapest quality name at 10x, off 28% - fits the V/MA toll-road, quality-plus-value wheelhouse.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D213" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: A scheduled job printed PYPL +3.9% (with V +3.0%, KO +8.7%) above verified prices, all one direction - same failure signature as the earlier MSFT $381 incident; reverted.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Watchlist name only - no held position was affected by the bad refresh.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C214" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D214" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  SOFI appears among the pre-dashboard closed exits (with TTD, MELI, APP, HOOD) in the group P&amp;L view.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Its blank EV/EBITDA and -$6.3B free cash flow are correct, not broken: SoFi is a lender, negative FCF is loan-book growth; judge it on ROE/ROIC and net margin, both strong.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B215" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C215" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  SOFI is one of 12 watchlist-only names consuming the free price-feed entitlement while $242K of actually-held stock goes unpriced.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C216" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Verdict: avoid. Rated Hold at $18.25 with only +9% upside - six firms CUT their targets after a beat, a sign the beat did not matter.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C217" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  SOUN (SoundHound AI) added to the Digital Platform group at the Aug 6 close $7.08. A small voice-AI company - drive-thru ordering, in-car assistants, AI call-centre agents. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Record Q2 (Aug 5): revenue $61.9M +45%, margins improving, full-year outlook RAISED to $230-260M. It has $203M cash and almost no debt, so plenty of runway. Stock jumped 10% on the news.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Still loses a lot of money: -67% net margin, burning ~$142M cash a year, no P/E. You're buying a growth story, not profits - and it's priced at 15x sales while unprofitable.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: Extreme-risk profile: 43% of its shares are sold short (one of the most-shorted stocks anywhere), beta 2.8, and it trades at $7 vs a 52-week range of $5.65-$22. Very volatile - a speculative bet, not a core holding.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C218" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C219" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The July 4-for-1 CRWD split was never applied to the manual record: the sheet showed CrowdStrike as the second-worst loser at -51% when it is actually up about +95%.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Fix is one row: 40 shares at $97.98 average cost, which ties the sheet to the broker to the dollar; the dashboard had already split-adjusted CRWD.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ CRWD is up +108%, helping make Software (+56%) one of the best-performing groups.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  A new Cybersecurity group was created: CRWD moved there with PANW, ZS, NET and FTNT — CRWD and ZS read as scaled but barely profitable platform players.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Minor drift: trimming $5.00 of commission from the CRWD cost row is part of a $254 fix to make the sheet match the broker to the cent.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D221" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  FTNT added to the board with ZS and NET, then moved into a new 16-name-era Cybersecurity group alongside CRWD, PANW, ZS and NET.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ It is the group's quality anchor - the only profitable one: 27% net margin, 132% ROE, 80% gross margin, $2.4B of real free cash flow; at 49x forward not cheap, but a cash machine.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C222" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C223" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Verdict: skip. After doubling this year (+104%), the average analyst target of $131.78 sits 19% BELOW the $161.95 price, and it trades at 49x forward earnings.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ The business is strong: Jul 29 quarter had revenue $2.05B up 26%, billings up 33%, earnings up 41%, and raised full-year guidance - hence the stock near its high at $168.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Dad's limits are far away: his $130 limit is near the Street's fair value but 25% below market; his sub-$100 limit is 40.6% below - anchored to an old price; nothing triggered.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C224" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D224" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Cloudflare flagged as the single most expensive name in the ~100-stock book: 202x forward P/E, ~860x EV/EBITDA, ~40x sales - priced for flawless execution.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Fastest grower in the cyber group at +34%, expanding into AI-inference at the edge - but a momentum bet, not a value one.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved with CRWD, PANW, ZS and FTNT into a new dedicated Cybersecurity group, making the valuation spread across the five obvious.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B225" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C225" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D225" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D226" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  PANW, first filed under Chips Manufacturing per the handwritten note, moved into a new Cybersecurity group with CRWD, ZS, NET and FTNT.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Within the cyber group, FTNT and PANW stand out as the profitable, cash-generating incumbents versus 32x-200x forward growth peers with similar ~25-34% growth.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B227" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C227" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D227" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  RBRK (Rubrik) added to the Cybersecurity group at $80.99 - watchlist only, no money in it.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Jumped 8.4% on Aug 4 when Loop Capital initiated coverage with a Buy and a $100 target.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Still loses money and has negative shareholder equity, so its ROE and debt ratios are shown blank.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Price sources conflicted ($80.99 vs $79.64); $80.99 was used since Google Finance agrees and it matches the reported +8.36% move exactly.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D228" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ZS added to the board (tipping it to 100 tickers), then moved into the new Cybersecurity group with CRWD, PANW, NET and FTNT.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ ZS is the more reasonable entry of the unprofitable cyber names: best Rule of 40 (56), $960M FCF-positive at breakeven, and already down 58% from its high.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  The group makes the valuation spread obvious: ~32x forward for Zscaler vs ~200x for Cloudflare at similar 25-34% growth.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C229" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  BWXT's Aug 3 after-market earnings were picked up by the overnight refresh and merged cleanly - all dashboard checks passed (110 stocks, 47 held, totals unchanged).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  BWXT is crossed out on Dad's note, so it was treated as cancelled and excluded from the buy recommendation.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: CNN quoted BWXT at $205 vs the correct $173.79; the bad source was discarded and prices cross-checked via stockanalysis.com and Google Finance.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C230" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Called the cleanest way to play the nuclear buildout without SMR execution risk: actual uranium, actual profit, +113% EPS growth, ~50% analyst upside (avg target $131).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Not cheap at 60x forward earnings.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Named alongside NEE as the conviction picks for real capital in the energy group; SMR/storage names only as small, sized-to-lose speculation.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B231" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C231" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D231" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  CEG reports earnings Aug 6 (VST, also held, reports Aug 7); advice is to wait for both prints before adding anything on the power/energy side.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ CEG declared a dividend of $0.4265 per share on the morning of Aug 5.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Keep about $5,150 in reserve so a post-earnings selloff in CEG or VST can be bought.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>LEU</t>
+        </is>
+      </c>
+      <c r="B233" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C233" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  LEU (Centrus Energy) added to Nuclear Energy at the Aug 7 close $191.37. The only US-owned uranium ENRICHER - makes HALEU fuel for next-gen/small reactors. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Profitable and strategically vital: revenue $474M, 10% net margin, a $4.5B order backlog through 2040, a $900M US government HALEU award, and $1.87B cash.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Expensive and volatile: 88x earnings, negative free cash flow (heavy plant spending), 26% of shares sold short, and it swings hugely - 52-week range $142 to $464. Dropped 5% on earnings then bounced 7% next day.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D234" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  OKLO added to the Energy group as a watchlist name among eight energy additions (SMRs, uranium, solar/storage, a utility), with ~$40K reserved for Energy buys.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Warning: OKLO is one of five names with essentially no profits and little revenue - valuation columns are blank; treat as a thematic call option and size it like a venture bet.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Do not read OKLO at -75% off its high as cheap - down a lot is not cheap with no earnings floor; only small, sized-to-lose speculation (CCJ or NEE for conviction instead).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C237" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C238" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- SMR is one of five energy names (with OKLO, NNE, TE, EOSE) with essentially no profits — valuation columns blank; thematic call options to be sized like venture bets.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Warning: do not read OKLO/SMR at -75%/-83% off highs as cheap — down a lot is not the same as cheap when there is no earnings floor underneath.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  For real capital in the group, CCJ or NEE were preferred; the SMR-type names only as small, sized-to-lose speculative positions.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>UUUU</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C239" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  UUUU (Energy Fuels) added to Nuclear Energy at the Aug 6 close $12.90 (rebounded ~10% Aug 7). A US uranium miner that also processes rare-earth elements at its Utah mill. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Strong balance sheet: ~$996M working capital (cash + marketable securities), producing real uranium (865k lbs last quarter, sold at $80/lb) and building a rare-earths plant.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Loses money today: -77% net margin, EPS -$0.34, burning ~$120M cash a year. No P/E - you're buying the uranium/rare-earth theme, not profits. 20% of shares are sold short.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D240" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- VST fell 8.15% to $143.23 - the worst day among the holdings; the drop was confirmed by POEMS and Google Finance against one source claiming $145.46.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VST reports Friday Aug 7 (CEG Aug 6); advice: keep ~$5,150 in reserve and wait for both prints before adding on the power/energy side.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VST moved from Energy to Nuclear Energy group (we own 42 sh, cost $6,078, budget $10,000) - its P&amp;L now reports under Nuclear Energy.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 changes: AXON (Axon Enterprise, NASDAQ - Tasers, body cameras, drones/counter-drone and evidence software for public safety) added to Drone &amp; Defense at the Aug 6, 2026 close 522.46, DOWN 14.28% on the day, header stamped "At close: Aug 6, 2026, 4:00 PM EDT" and confirmed by MarketBeat; note ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C242" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  XE (X-Energy) deliberately left at Monday's Aug 3 close - no trustworthy fresh close was available; the staleness is disclosed on the dashboard; watchlist only, no position.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy to Nuclear Energy (X-energy is a nuclear/small-reactor developer, so it belongs there). Group label only.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B243" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C243" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The $300 buy limit sits below Eaton's 52-week low of $311.92 - it waits for ground untouched in a year; analyst average is $455.79, 52% above the desired entry.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Checksum caught a transcription error: ETN was keyed 386.20 vs actual 386.26; fixed, and earnings-related fundamentals refresh on ETN preserved.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B245" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C245" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C246" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B247" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C247" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  GEV (2 shares, $2,147.30 cost) moved with ETN into a new Power and Electrification group; totals unchanged to the cent, nothing bought or sold.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- GE Vernova JV partner AirJoule: genuinely operating (unit installed Jul 28, Kubota deal Jul 21) but no revenue, 16 employees and a $46M funding hole - a ticket, not a position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>HUBB</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D248" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Hubbell was pulled fresh onto the dashboard and joined the new Power &amp; Electrification group as a watchlist name at $502.24.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ It beat and raised on grid modernization and data centres - the steadiest, lowest-volatility of the four new power names.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  None of Dad's nine buy limits are triggered; Hubbell is the closest, still 14.4% above his $430 line, with about +20% to the analyst target.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>HYLN</t>
+        </is>
+      </c>
+      <c r="B249" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C249" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D249" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  HYLN (Hyliion) added to Power &amp; Electrification at the Aug 7 close $3.87. Makes the KARNO generator - a fuel-flexible power module. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: Pre-revenue in practice: only $5.8M sales, so its price-to-sales (121x) is meaningless and it burns ~$64M/yr. Very volatile (beta 3.6). A bet on a technology, not a business yet.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Momentum from defence: won a $41.7M US Navy award to scale its power modules and demonstrated them running as one plant. $72M cash. 3 analysts Buy, avg $7. Q2 call Aug 12.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C250" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D250" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B251" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C251" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D251" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: Advisor admitted MPWR's 'live' price was filled in from memory, not retrieved; on a proper re-pull, four of five such prices were wrong.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Jumped 10.6% overnight, blowing straight through the standing buy limit - the entry moved further away.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Earnings-related fundamentals refresh on MPWR preserved during a data cleanup.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C252" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Energy group cleaned up: MPWR now sits in a tighter 12-name electrification-and-power bucket with ETN, VRT, GEV, VST, NEE.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MPWR moved from Energy to Power &amp; Electrification group (we own 1 sh, cost $1,538.56, budget $5,000) - its P&amp;L now reports under Power &amp; Electrification. It makes power-management chips for AI/data-centre boards.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 move: MPWR (Monolithic Power Systems, HELD - 1 sh / 1,538.56 cost / 5,000 budget) moved Energy -&gt; Power and Electrification per request. Field values, position and budget untouched; group P&amp;L attribution now reports under Power and Electrification. Energy 11 -&gt; 10 names, Power and ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="B253" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C253" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D253" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NVT (nVent Electric) added at $162.24 as watchlist-only in the new six-name Power and Electrification group (which also absorbed held positions ETN and GEV).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ nVent has raised full-year guidance twice on AI liquid-cooling demand and is buying back its own shares.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: sources disagreed on the close ($162.24 vs $163.68); $162.24 was stored on a two-sources-to-one basis.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>POWI</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C254" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  POWI (Power Integrations) added to Power &amp; Electrification at the Aug 7 close $64.59. Makes energy-efficient power-conversion chips for industry, renewables and AI. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Rock-solid balance sheet (no debt, pays a dividend), 54% gross margins, and Q2 beat and jumped ~9%. A quality niche chipmaker levered to grid/renewables demand.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Barely profitable right now, so the P/E (147) and EV/EBITDA (80) look extreme; you're paying up for a recovery. Only 5 analysts, avg target $77. Stock $65 vs a $91 high.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="inlineStr">
+        <is>
+          <t>POWL</t>
+        </is>
+      </c>
+      <c r="B255" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C255" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Powell Industries missed on both revenue and profit Aug 3, gapping down almost 13% before closing -3.8%; with only four analysts covering it, the price moves violently.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ The order book tells the opposite story: new orders +158%, backlog +69%, and a 3.0x book-to-bill - three dollars booked for every dollar shipped.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Watchlist-only in the new Power &amp; Electrification group at $211.38; an implausible 122.6% return-on-capital figure was rejected for the conservative 38.4%.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B256" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D256" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  PWR added watchlist-only to the new 'Power and Electrification' group alongside POWL, NVT and HUBB.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Quanta Services ($693) beat big on Jul 30 and raised full-year guidance - revenue +41%, backlog $53.4B; the stock jumped 13.65% that day.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>AIRJ</t>
+        </is>
+      </c>
+      <c r="B257" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C257" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D257" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- AIRJ is filed under Energy but is really an industrial equipment maker (atmospheric water capture); a lottery ticket, and its news is about drinking water, not energy.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Real traction: 50/50 JV with GE Vernova is operating (unit installed at GE's NY campus Jul 28); Kubota signed as exclusive US residential partner Jul 21, stock +15% that day.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Balance sheet is clean: $35M cash, no debt, funded into 2028; all five covering analysts have targets above the price (lowest $6.00 vs $5.95).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- But there is no revenue at all - advisor's verdict: interesting, not a buy today.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: the $5.84 Aug 4 close comes from a single source; no second source had that day's data.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: AIRJ was already in Energy, so the regrouping request needed no action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C258" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
+        <is>
+          <t>FLNC</t>
+        </is>
+      </c>
+      <c r="B259" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C259" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D259" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: FLNC missed Q3 badly on Aug 5: revenue $649.8M vs $806.2M expected (-19.4%), EPS -$0.24 vs +$0.02, full-year guidance cut to $2.9-3.1B from $3.2-3.6B; shares fell to ~$10.89.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Verdict: a falling knife — do not buy; analysts will cut forecasts and the stock likely has further to fall.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The $14.23 stored on the dashboard is the pre-release close and is stale; sources also disagree on FLNC's market cap ($1.43B-$2.62B), EPS, ROE and net margin.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  FLNC had just been added to the Energy group at the Aug 5 close of $14.23 before the report; the next refresh will capture the gap down.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>MYRG</t>
+        </is>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C260" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D260" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MYRG (MYR Group - you wrote 'MYR') added to the new Renewal Energy group at the Aug 7 close $337.42. An electrical-infrastructure builder: power lines, substations and data-centre/grid electrical work. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ High quality and profitable: revenue $4B (+16%), earnings more than doubled to $10.54/share, 25% return on capital, positive cash flow, almost no debt. Record Q2 and record $3.16B backlog.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Direct beneficiary of the grid buildout and data-centre electrification wave. Analysts see meaningful upside (avg ~$423 vs ~$337). Trades at a reasonable ~26x forward earnings for the growth.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- A contractor, so margins are thin (~4% net) and results can be lumpy project to project; the stock has pulled back from a $503 high.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B261" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C261" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ NEE is the only dividend-quality name in the group: a $187B regulated utility plus the largest US renewables developer, 32% margins, near the ~$99 analyst fair value.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ For real capital in the nuclear/energy group: CCJ or NEE for conviction; the SMR and storage names only as small, sized-to-lose speculative bets.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C262" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NEE now sits in the cleaner electrification-and-power-equipment bucket (with ETN, VRT, GEV, VST, MPWR) after the Energy group was trimmed from 18 names to 12.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B263" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C263" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NRG (NRG Energy) added to Energy at the Aug 6 close $119.05. A big Texas power company - it generates electricity, sells it to homes, and is now a major play on data-centre/AI power demand. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Real, profitable business paying a ~1.6% dividend: $33B revenue, earnings up 76% to $3.87/share, 24% return on equity. Cheap on next year's earnings (~12x) with a bargain PEG of 0.5.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Growth catalyst: on its Aug 4 call it announced a landmark 1.2-gigawatt deal (expandable to 2.4GW) to power a hyperscaler's data centre in Texas - ~$500M/yr of profit once running, ~2029.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Heavily indebted (debt is ~5x equity - normal for a utility but real), and free cash flow is thin, so it looks expensive on a cash-flow basis (72x). Management sees this year's profit below the mid-point on soft Texas power prices.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Analysts still like it (~$194 avg target vs $119 now) but two firms trimmed targets on Aug 5; the stock touched a 52-week low ($112.50) recently. The $119.05 stored is the Aug 6 close - tonight's refresh confirms it.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C264" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- VRT reports earnings within a week - buying now means holding a binary event within days, which is why the week's buy pick went elsewhere.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Per-firm analyst rating actions for mid-caps like VRT need the FMP Starter plan (~$22-29/month); the upgrade was recommended as worthwhile.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B265" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C265" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D265" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C266" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D266" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VRT now sits in the cleaner electrification-and-power-equipment bucket after the Energy group regrouping (18 names down to 12).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="inlineStr">
+        <is>
           <t>AFRM</t>
         </is>
       </c>
-      <c r="B203" s="10" t="inlineStr">
+      <c r="B267" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C203" s="12" t="inlineStr">
+      <c r="C267" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr">
+      <c r="D267" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17224,394 +19877,81 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="10" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B204" s="10" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C268" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="B269" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C204" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D204" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- COIN sits with HOOD/AFRM/SHOP as a momentum-and-story name where valuation still has a long way to fall if growth blinks - do not bucket it with V/MA/PYPL quality names.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="10" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="B205" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C205" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D205" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Q2 brought a third straight quarterly loss; the stock dropped 13.4% and TTM earnings turned negative, nulling P/E, forward P/E, PEG, EV/EBITDA and Rule-of-40.
-</t>
-          </r>
+      <c r="C269" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D269" s="10" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  Dad's item #8 was read as COIN with a $300 limit vs a $164 price - inconsistent with his other limits (7-39% below market); likely a typo or misread, needs confirming.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: the official Jul 31 close was $146.26 (-10.59%); several sources showed undated or wrong figures (one said -8.03%), so prices were verified via post-close articles.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="B206" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C206" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D206" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Fiserv is the hardest flag in the fintech group: down 71% from its high at 6x forward - a potential value trap, not a bargain; growth decelerating with guidance cuts.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Advisor recommends a deep-dive to settle the value-trap question before anyone acts on the low multiple.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="10" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="B207" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C207" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D207" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Housekeeping error: Fiserv moved to Nasdaq and changed ticker to FISV (announced Oct 29, 2025); the board still shows FI, so its quote may be mismatched - fix due on next push.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="10" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="B208" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C208" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D208" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  HOOD appears among the pre-dashboard closed trades (with TTD, MELI, APP, SOFI) captured in the new 'Closed / other' line of the group summary.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Framing: HOOD sits with COIN, AFRM and SHOP as momentum-and-story names where valuation still has a long way to fall if growth blinks — not with the V/MA/PYPL quality bucket.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="10" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="B209" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C209" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D209" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  HOOD's price was verified against a third outside source to break a tie between conflicting quotes during the data check.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="10" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="B210" s="10" t="inlineStr">
+            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C210" s="13" t="inlineStr">
+      <c r="C270" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D210" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ HOOD beat on July 29: revenue $1.31B (+32%) and EPS $0.62 vs $0.43 expected (a 44% beat), with almost no debt; it bottomed at $63.52 in March and has recovered 45% since.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ All 26 analyst targets sit above the $92.80 price (+32% implied upside); even the lowest target on the desk is $100 — you are not fighting the crowd.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  The 40% drawdown is read as cyclical, not structural: crypto trading revenue fell 38% with Bitcoin and Ethereum off their peaks and comes back when crypto recovers.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Bear case: HOOD trades at 16.5x revenue vs its 11.9x historical average — 30%+ downside if it merely reverts — and earnings depend on retail traders staying active.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Conviction Medium, 6-24 month horizon; the thesis breaks if monthly funded customers fall for two straight quarters.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="10" t="inlineStr">
-        <is>
-          <t>LMND</t>
-        </is>
-      </c>
-      <c r="B211" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C211" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D211" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Lemonade's report showed its loss ratio improving from 78% to 62% with fewer staff; rated 4 of 5 with +27% to target - but small, volatile and still loss-making.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Flagged as one of two genuinely new AI-beneficiary ideas (small, speculative); added to Fintech/Digital Platform at $54.11 after two independent sources confirmed the price.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="10" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B212" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C212" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D212" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Mastercard is filed with the elite compounders: 27x earnings, +17% growth, 100% gross margin and a 232% return on equity.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t>MELI</t>
-        </is>
-      </c>
-      <c r="B213" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C213" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D213" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="10" t="inlineStr">
-        <is>
-          <t>MELI</t>
-        </is>
-      </c>
-      <c r="B214" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C214" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D214" s="10" t="inlineStr">
+      <c r="D270" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17637,316 +19977,124 @@
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>- Risk: MELI fell because its numbers got worse - when analysts update they will cut forecasts, so the stock likely has further to adjust downward.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="10" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="B215" s="10" t="inlineStr">
+            <t xml:space="preserve">- Risk: MELI fell because its numbers got worse - when analysts update they will cut forecasts, so the stock likely has further to adjust downward.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="10" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B271" s="10" t="inlineStr">
         <is>
           <t>2026-07-20  (Jul 20-26, 2026)</t>
         </is>
       </c>
-      <c r="C215" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D215" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Tagged the deep-value pick of the fintech group: cheapest quality name at 10x, off 28% - fits the V/MA toll-road, quality-plus-value wheelhouse.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="10" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="B216" s="10" t="inlineStr">
+      <c r="C271" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C272" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D272" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="10" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B273" s="10" t="inlineStr">
         <is>
           <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
         </is>
       </c>
-      <c r="C216" s="12" t="inlineStr">
+      <c r="C273" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D273" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B274" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C274" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D216" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: A scheduled job printed PYPL +3.9% (with V +3.0%, KO +8.7%) above verified prices, all one direction - same failure signature as the earlier MSFT $381 incident; reverted.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Watchlist name only - no held position was affected by the bad refresh.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="10" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B217" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C217" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D217" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B218" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C218" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D218" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  SOFI appears among the pre-dashboard closed exits (with TTD, MELI, APP, HOOD) in the group P&amp;L view.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Its blank EV/EBITDA and -$6.3B free cash flow are correct, not broken: SoFi is a lender, negative FCF is loan-book growth; judge it on ROE/ROIC and net margin, both strong.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="10" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B219" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C219" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D219" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  SOFI is one of 12 watchlist-only names consuming the free price-feed entitlement while $242K of actually-held stock goes unpriced.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="10" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B220" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C220" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D220" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Verdict: avoid. Rated Hold at $18.25 with only +9% upside - six firms CUT their targets after a beat, a sign the beat did not matter.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="10" t="inlineStr">
-        <is>
-          <t>SOUN</t>
-        </is>
-      </c>
-      <c r="B221" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C221" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D221" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  SOUN (SoundHound AI) added to the Digital Platform group at the Aug 6 close $7.08. A small voice-AI company - drive-thru ordering, in-car assistants, AI call-centre agents. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Record Q2 (Aug 5): revenue $61.9M +45%, margins improving, full-year outlook RAISED to $230-260M. It has $203M cash and almost no debt, so plenty of runway. Stock jumped 10% on the news.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Still loses a lot of money: -67% net margin, burning ~$142M cash a year, no P/E. You're buying a growth story, not profits - and it's priced at 15x sales while unprofitable.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: Extreme-risk profile: 43% of its shares are sold short (one of the most-shorted stocks anywhere), beta 2.8, and it trades at $7 vs a 52-week range of $5.65-$22. Very volatile - a speculative bet, not a core holding.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B222" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C222" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D222" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="10" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B223" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C223" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D223" s="10" t="inlineStr">
+      <c r="D274" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17963,2094 +20111,22 @@
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>- If two or three more large firms follow Uber in admitting they cannot trace AI spending to output, the whole 'AI as margin lever' thesis needs rethinking.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B224" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C224" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D224" s="10" t="inlineStr">
-        <is>
+            <t xml:space="preserve">- If two or three more large firms follow Uber in admitting they cannot trace AI spending to output, the whole 'AI as margin lever' thesis needs rethinking.
+</t>
+          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="10" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B225" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C225" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D225" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The July 4-for-1 CRWD split was never applied to the manual record: the sheet showed CrowdStrike as the second-worst loser at -51% when it is actually up about +95%.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Fix is one row: 40 shares at $97.98 average cost, which ties the sheet to the broker to the dollar; the dashboard had already split-adjusted CRWD.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ CRWD is up +108%, helping make Software (+56%) one of the best-performing groups.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  A new Cybersecurity group was created: CRWD moved there with PANW, ZS, NET and FTNT — CRWD and ZS read as scaled but barely profitable platform players.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Minor drift: trimming $5.00 of commission from the CRWD cost row is part of a $254 fix to make the sheet match the broker to the cent.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B226" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C226" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D226" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B227" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C227" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D227" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  FTNT added to the board with ZS and NET, then moved into a new 16-name-era Cybersecurity group alongside CRWD, PANW, ZS and NET.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ It is the group's quality anchor - the only profitable one: 27% net margin, 132% ROE, 80% gross margin, $2.4B of real free cash flow; at 49x forward not cheap, but a cash machine.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B228" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C228" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D228" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B229" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C229" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D229" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Verdict: skip. After doubling this year (+104%), the average analyst target of $131.78 sits 19% BELOW the $161.95 price, and it trades at 49x forward earnings.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ The business is strong: Jul 29 quarter had revenue $2.05B up 26%, billings up 33%, earnings up 41%, and raised full-year guidance - hence the stock near its high at $168.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Dad's limits are far away: his $130 limit is near the Street's fair value but 25% below market; his sub-$100 limit is 40.6% below - anchored to an old price; nothing triggered.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C230" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D230" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Cloudflare flagged as the single most expensive name in the ~100-stock book: 202x forward P/E, ~860x EV/EBITDA, ~40x sales - priced for flawless execution.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Fastest grower in the cyber group at +34%, expanding into AI-inference at the edge - but a momentum bet, not a value one.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved with CRWD, PANW, ZS and FTNT into a new dedicated Cybersecurity group, making the valuation spread across the five obvious.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="10" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="B231" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C231" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D231" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C232" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D232" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  PANW, first filed under Chips Manufacturing per the handwritten note, moved into a new Cybersecurity group with CRWD, ZS, NET and FTNT.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Within the cyber group, FTNT and PANW stand out as the profitable, cash-generating incumbents versus 32x-200x forward growth peers with similar ~25-34% growth.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="10" t="inlineStr">
-        <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="B233" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C233" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D233" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  RBRK (Rubrik) added to the Cybersecurity group at $80.99 - watchlist only, no money in it.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Jumped 8.4% on Aug 4 when Loop Capital initiated coverage with a Buy and a $100 target.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Still loses money and has negative shareholder equity, so its ROE and debt ratios are shown blank.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Price sources conflicted ($80.99 vs $79.64); $80.99 was used since Google Finance agrees and it matches the reported +8.36% move exactly.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>ZS</t>
-        </is>
-      </c>
-      <c r="B234" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C234" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D234" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ZS added to the board (tipping it to 100 tickers), then moved into the new Cybersecurity group with CRWD, PANW, NET and FTNT.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ ZS is the more reasonable entry of the unprofitable cyber names: best Rule of 40 (56), $960M FCF-positive at breakeven, and already down 58% from its high.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  The group makes the valuation spread obvious: ~32x forward for Zscaler vs ~200x for Cloudflare at similar 25-34% growth.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t>BWXT</t>
-        </is>
-      </c>
-      <c r="B235" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C235" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D235" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  BWXT's Aug 3 after-market earnings were picked up by the overnight refresh and merged cleanly - all dashboard checks passed (110 stocks, 47 held, totals unchanged).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  BWXT is crossed out on Dad's note, so it was treated as cancelled and excluded from the buy recommendation.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: CNN quoted BWXT at $205 vs the correct $173.79; the bad source was discarded and prices cross-checked via stockanalysis.com and Google Finance.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="10" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="B236" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C236" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D236" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Called the cleanest way to play the nuclear buildout without SMR execution risk: actual uranium, actual profit, +113% EPS growth, ~50% analyst upside (avg target $131).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Not cheap at 60x forward earnings.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Named alongside NEE as the conviction picks for real capital in the energy group; SMR/storage names only as small, sized-to-lose speculation.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="B237" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C237" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D237" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>CEG</t>
-        </is>
-      </c>
-      <c r="B238" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C238" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D238" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  CEG reports earnings Aug 6 (VST, also held, reports Aug 7); advice is to wait for both prints before adding anything on the power/energy side.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ CEG declared a dividend of $0.4265 per share on the morning of Aug 5.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Keep about $5,150 in reserve so a post-earnings selloff in CEG or VST can be bought.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
-        <is>
-          <t>LEU</t>
-        </is>
-      </c>
-      <c r="B239" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C239" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D239" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  LEU (Centrus Energy) added to Nuclear Energy at the Aug 7 close $191.37. The only US-owned uranium ENRICHER - makes HALEU fuel for next-gen/small reactors. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Profitable and strategically vital: revenue $474M, 10% net margin, a $4.5B order backlog through 2040, a $900M US government HALEU award, and $1.87B cash.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Expensive and volatile: 88x earnings, negative free cash flow (heavy plant spending), 26% of shares sold short, and it swings hugely - 52-week range $142 to $464. Dropped 5% on earnings then bounced 7% next day.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="B240" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C240" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D240" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="10" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="B241" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C241" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D241" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="B242" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C242" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D242" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  OKLO added to the Energy group as a watchlist name among eight energy additions (SMRs, uranium, solar/storage, a utility), with ~$40K reserved for Energy buys.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Warning: OKLO is one of five names with essentially no profits and little revenue - valuation columns are blank; treat as a thematic call option and size it like a venture bet.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Do not read OKLO at -75% off its high as cheap - down a lot is not cheap with no earnings floor; only small, sized-to-lose speculation (CCJ or NEE for conviction instead).</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="B243" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C243" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>SMR</t>
-        </is>
-      </c>
-      <c r="B244" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C244" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D244" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- SMR is one of five energy names (with OKLO, NNE, TE, EOSE) with essentially no profits — valuation columns blank; thematic call options to be sized like venture bets.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Warning: do not read OKLO/SMR at -75%/-83% off highs as cheap — down a lot is not the same as cheap when there is no earnings floor underneath.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  For real capital in the group, CCJ or NEE were preferred; the SMR-type names only as small, sized-to-lose speculative positions.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>UUUU</t>
-        </is>
-      </c>
-      <c r="B245" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C245" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  UUUU (Energy Fuels) added to Nuclear Energy at the Aug 6 close $12.90 (rebounded ~10% Aug 7). A US uranium miner that also processes rare-earth elements at its Utah mill. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Strong balance sheet: ~$996M working capital (cash + marketable securities), producing real uranium (865k lbs last quarter, sold at $80/lb) and building a rare-earths plant.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Loses money today: -77% net margin, EPS -$0.34, burning ~$120M cash a year. No P/E - you're buying the uranium/rare-earth theme, not profits. 20% of shares are sold short.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C246" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="10" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B247" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C247" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D247" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- VST fell 8.15% to $143.23 - the worst day among the holdings; the drop was confirmed by POEMS and Google Finance against one source claiming $145.46.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VST reports Friday Aug 7 (CEG Aug 6); advice: keep ~$5,150 in reserve and wait for both prints before adding on the power/energy side.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VST moved from Energy to Nuclear Energy group (we own 42 sh, cost $6,078, budget $10,000) - its P&amp;L now reports under Nuclear Energy.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 changes: AXON (Axon Enterprise, NASDAQ - Tasers, body cameras, drones/counter-drone and evidence software for public safety) added to Drone &amp; Defense at the Aug 6, 2026 close 522.46, DOWN 14.28% on the day, header stamped "At close: Aug 6, 2026, 4:00 PM EDT" and confirmed by MarketBeat; note ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>XE</t>
-        </is>
-      </c>
-      <c r="B248" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C248" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D248" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  XE (X-Energy) deliberately left at Monday's Aug 3 close - no trustworthy fresh close was available; the staleness is disclosed on the dashboard; watchlist only, no position.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy to Nuclear Energy (X-energy is a nuclear/small-reactor developer, so it belongs there). Group label only.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B249" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C249" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D249" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B250" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C250" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D250" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The $300 buy limit sits below Eaton's 52-week low of $311.92 - it waits for ground untouched in a year; analyst average is $455.79, 52% above the desired entry.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Checksum caught a transcription error: ETN was keyed 386.20 vs actual 386.26; fixed, and earnings-related fundamentals refresh on ETN preserved.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C251" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D251" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="10" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B252" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C252" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D252" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="10" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B253" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C253" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  GEV (2 shares, $2,147.30 cost) moved with ETN into a new Power and Electrification group; totals unchanged to the cent, nothing bought or sold.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- GE Vernova JV partner AirJoule: genuinely operating (unit installed Jul 28, Kubota deal Jul 21) but no revenue, 16 employees and a $46M funding hole - a ticket, not a position.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="10" t="inlineStr">
-        <is>
-          <t>HUBB</t>
-        </is>
-      </c>
-      <c r="B254" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C254" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D254" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Hubbell was pulled fresh onto the dashboard and joined the new Power &amp; Electrification group as a watchlist name at $502.24.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ It beat and raised on grid modernization and data centres - the steadiest, lowest-volatility of the four new power names.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  None of Dad's nine buy limits are triggered; Hubbell is the closest, still 14.4% above his $430 line, with about +20% to the analyst target.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="10" t="inlineStr">
-        <is>
-          <t>HYLN</t>
-        </is>
-      </c>
-      <c r="B255" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C255" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D255" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  HYLN (Hyliion) added to Power &amp; Electrification at the Aug 7 close $3.87. Makes the KARNO generator - a fuel-flexible power module. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: Pre-revenue in practice: only $5.8M sales, so its price-to-sales (121x) is meaningless and it burns ~$64M/yr. Very volatile (beta 3.6). A bet on a technology, not a business yet.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Momentum from defence: won a $41.7M US Navy award to scale its power modules and demonstrated them running as one plant. $72M cash. 3 analysts Buy, avg $7. Q2 call Aug 12.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B256" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C256" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D256" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B257" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C257" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: Advisor admitted MPWR's 'live' price was filled in from memory, not retrieved; on a proper re-pull, four of five such prices were wrong.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Jumped 10.6% overnight, blowing straight through the standing buy limit - the entry moved further away.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Earnings-related fundamentals refresh on MPWR preserved during a data cleanup.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B258" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C258" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D258" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Energy group cleaned up: MPWR now sits in a tighter 12-name electrification-and-power bucket with ETN, VRT, GEV, VST, NEE.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MPWR moved from Energy to Power &amp; Electrification group (we own 1 sh, cost $1,538.56, budget $5,000) - its P&amp;L now reports under Power &amp; Electrification. It makes power-management chips for AI/data-centre boards.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 move: MPWR (Monolithic Power Systems, HELD - 1 sh / 1,538.56 cost / 5,000 budget) moved Energy -&gt; Power and Electrification per request. Field values, position and budget untouched; group P&amp;L attribution now reports under Power and Electrification. Energy 11 -&gt; 10 names, Power and ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="10" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="B259" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C259" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D259" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NVT (nVent Electric) added at $162.24 as watchlist-only in the new six-name Power and Electrification group (which also absorbed held positions ETN and GEV).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ nVent has raised full-year guidance twice on AI liquid-cooling demand and is buying back its own shares.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: sources disagreed on the close ($162.24 vs $163.68); $162.24 was stored on a two-sources-to-one basis.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="10" t="inlineStr">
-        <is>
-          <t>POWI</t>
-        </is>
-      </c>
-      <c r="B260" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C260" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D260" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  POWI (Power Integrations) added to Power &amp; Electrification at the Aug 7 close $64.59. Makes energy-efficient power-conversion chips for industry, renewables and AI. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Rock-solid balance sheet (no debt, pays a dividend), 54% gross margins, and Q2 beat and jumped ~9%. A quality niche chipmaker levered to grid/renewables demand.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Barely profitable right now, so the P/E (147) and EV/EBITDA (80) look extreme; you're paying up for a recovery. Only 5 analysts, avg target $77. Stock $65 vs a $91 high.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="10" t="inlineStr">
-        <is>
-          <t>POWL</t>
-        </is>
-      </c>
-      <c r="B261" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C261" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D261" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Powell Industries missed on both revenue and profit Aug 3, gapping down almost 13% before closing -3.8%; with only four analysts covering it, the price moves violently.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ The order book tells the opposite story: new orders +158%, backlog +69%, and a 3.0x book-to-bill - three dollars booked for every dollar shipped.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Watchlist-only in the new Power &amp; Electrification group at $211.38; an implausible 122.6% return-on-capital figure was rejected for the conservative 38.4%.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>PWR</t>
-        </is>
-      </c>
-      <c r="B262" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C262" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D262" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  PWR added watchlist-only to the new 'Power and Electrification' group alongside POWL, NVT and HUBB.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Quanta Services ($693) beat big on Jul 30 and raised full-year guidance - revenue +41%, backlog $53.4B; the stock jumped 13.65% that day.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="10" t="inlineStr">
-        <is>
-          <t>AIRJ</t>
-        </is>
-      </c>
-      <c r="B263" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C263" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- AIRJ is filed under Energy but is really an industrial equipment maker (atmospheric water capture); a lottery ticket, and its news is about drinking water, not energy.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Real traction: 50/50 JV with GE Vernova is operating (unit installed at GE's NY campus Jul 28); Kubota signed as exclusive US residential partner Jul 21, stock +15% that day.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Balance sheet is clean: $35M cash, no debt, funded into 2028; all five covering analysts have targets above the price (lowest $6.00 vs $5.95).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- But there is no revenue at all - advisor's verdict: interesting, not a buy today.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: the $5.84 Aug 4 close comes from a single source; no second source had that day's data.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: AIRJ was already in Energy, so the regrouping request needed no action.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="B264" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C264" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D264" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="10" t="inlineStr">
-        <is>
-          <t>FLNC</t>
-        </is>
-      </c>
-      <c r="B265" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C265" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D265" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: FLNC missed Q3 badly on Aug 5: revenue $649.8M vs $806.2M expected (-19.4%), EPS -$0.24 vs +$0.02, full-year guidance cut to $2.9-3.1B from $3.2-3.6B; shares fell to ~$10.89.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Verdict: a falling knife — do not buy; analysts will cut forecasts and the stock likely has further to fall.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The $14.23 stored on the dashboard is the pre-release close and is stale; sources also disagree on FLNC's market cap ($1.43B-$2.62B), EPS, ROE and net margin.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  FLNC had just been added to the Energy group at the Aug 5 close of $14.23 before the report; the next refresh will capture the gap down.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="inlineStr">
-        <is>
-          <t>MYRG</t>
-        </is>
-      </c>
-      <c r="B266" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C266" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D266" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MYRG (MYR Group - you wrote 'MYR') added to the new Renewal Energy group at the Aug 7 close $337.42. An electrical-infrastructure builder: power lines, substations and data-centre/grid electrical work. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ High quality and profitable: revenue $4B (+16%), earnings more than doubled to $10.54/share, 25% return on capital, positive cash flow, almost no debt. Record Q2 and record $3.16B backlog.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Direct beneficiary of the grid buildout and data-centre electrification wave. Analysts see meaningful upside (avg ~$423 vs ~$337). Trades at a reasonable ~26x forward earnings for the growth.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- A contractor, so margins are thin (~4% net) and results can be lumpy project to project; the stock has pulled back from a $503 high.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="10" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B267" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C267" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D267" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ NEE is the only dividend-quality name in the group: a $187B regulated utility plus the largest US renewables developer, 32% margins, near the ~$99 analyst fair value.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ For real capital in the nuclear/energy group: CCJ or NEE for conviction; the SMR and storage names only as small, sized-to-lose speculative bets.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="10" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B268" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C268" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D268" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NEE now sits in the cleaner electrification-and-power-equipment bucket (with ETN, VRT, GEV, VST, MPWR) after the Energy group was trimmed from 18 names to 12.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="10" t="inlineStr">
-        <is>
-          <t>NRG</t>
-        </is>
-      </c>
-      <c r="B269" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C269" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D269" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NRG (NRG Energy) added to Energy at the Aug 6 close $119.05. A big Texas power company - it generates electricity, sells it to homes, and is now a major play on data-centre/AI power demand. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Real, profitable business paying a ~1.6% dividend: $33B revenue, earnings up 76% to $3.87/share, 24% return on equity. Cheap on next year's earnings (~12x) with a bargain PEG of 0.5.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Growth catalyst: on its Aug 4 call it announced a landmark 1.2-gigawatt deal (expandable to 2.4GW) to power a hyperscaler's data centre in Texas - ~$500M/yr of profit once running, ~2029.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Heavily indebted (debt is ~5x equity - normal for a utility but real), and free cash flow is thin, so it looks expensive on a cash-flow basis (72x). Management sees this year's profit below the mid-point on soft Texas power prices.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Analysts still like it (~$194 avg target vs $119 now) but two firms trimmed targets on Aug 5; the stock touched a 52-week low ($112.50) recently. The $119.05 stored is the Aug 6 close - tonight's refresh confirms it.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B270" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C270" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D270" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- VRT reports earnings within a week - buying now means holding a binary event within days, which is why the week's buy pick went elsewhere.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Per-firm analyst rating actions for mid-caps like VRT need the FMP Starter plan (~$22-29/month); the upgrade was recommended as worthwhile.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C271" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D271" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B272" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C272" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D272" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VRT now sits in the cleaner electrification-and-power-equipment bucket after the Energy group regrouping (18 names down to 12).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
           </r>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D272"/>
+  <autoFilter ref="A1:D274"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -52536,7 +52612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53360,8 +53436,25 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>7d7a250</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Aug 8 batch of 9 additions (all watchlist only, all at the Aug 7 2026 close, all stamped 'At close: Aug 7, 2026, 4:00 PM EDT'; jan2 and all-time highs NOT FOUND for every name - 52-week highs stored as ath proxies; where two analyst sources conflicted, stockanalysis was taken). COMPUTING CHIPS: ON (ON Semiconductor / onsemi) at 81.17 - power &amp; sensing chips for autos/industrial/AI data centres; profitable (rev 6.20B, EPS 1.56 +43.5%, ROIC 15.6%, FCF 1.5B) but trailing P/E 52 (forward 21, PEG 0.62); acquiring Synaptics ~7B announced Jun 25. NEOCLOUD WATCH: KEEL (Keel Infrastructure, NASDAQ) at 3.88 - a former crypto-miner PIVOTED to AI/HPC data centres; deeply unprofitable (net margin -171%, FCF -413M, EPS -0.65) with negative gross margin, beta 4.11, short interest ~17-18%; FY2026 revenue is estimated to FALL ~46% during the transition even though TTM shows +67%; 11 analysts Strong Buy avg 6.55; next earnings Aug 10. SPACE: SIDU (Sidus Space) at 2.24 - micro-cap 3D-printed AI satellite maker; revenue only 3.5M (declining), P/S ~64x (chart-scale outlier), all profitability deeply negative, ~170M raised over prior 6 months so cash-heavy/near debt-free but burning ~29M/yr; only 1 analyst (a Sell, no target - fvMin/fvAvg/fvMax left blank per the POET precedent); on the MDA SHIELD contract vehicle. POWER AND ELECTRIFICATION (user's 'Electricity Energy' -&gt; mapped to the existing Power and Electrification group): POWI (Power Integrations) at 64.59 - high-voltage power-conversion chips for industrial/renewables/AI; profitable but barely (net margin 5.6%), NO debt, dividend ~1.3%, trailing P/E 147 (forward 38.6) and EV/EBITDA 80 (mild chart-scale outlier); Q2 (Aug 5) beat, jumped ~9.5%. HYLN (Hyliion) at 3.87 - KARNO fuel-agnostic linear generator; pre-scale (revenue 5.8M, P/S 121x = chart-scale OUTLIER, net margin -888%, FCF -64M, cash 72M), beta 3.56; won a 41.7M US Navy award (Aug) to scale multi-megawatt modules; Q2 call Aug 12; 3 analysts Buy avg 7. DRONE &amp; DEFENCE (user's 'Drone' and 'defense' -&gt; both the existing Drone &amp; Defense group): RCAT (Red Cat) at 9.21 - military drone maker (Black Widow, won US Army SRR); pre-profit (net margin -136%, FCF ~-158M (conflicts with -97M on financials page), EPS -0.81) but 326M cash cushion; Q2 (Aug 6) was a DOUBLE MISS (rev 20.19M vs 22.79M, loss 0.26 vs 0.22 exp) yet stock closed +6.2% next day; short interest 23.6%; a short-seller (Fuzzy Panda) alleged overstated Army-contract size - flagged as risk. revG left blank (sources gave +459.8% vs +866.9%, irreconcilable; Q2 was +527% YoY). Plus the THREE big defence primes, all profitable dividend payers: LMT (Lockheed Martin) at 587.95 - F-35, THAAD/PAC-3 missiles; rev 77B, EPS 27.14 (+52.5% off 2025's program-loss base), P/E 21.7, ROE 89%, 35B THAAD award Jun 24; 21 analysts HOLD avg 629.53 (Goldman at Sell 503). RTX (RTX Corp / Raytheon) at 223.03 - Collins Aerospace + Pratt &amp; Whitney + Raytheon missiles (Patriot, AIM-9X); rev 93.5B, richest of the three at P/E 39 / EV-EBITDA 22, dividend 1.3%, backlog 289B; sits ~1% below its 52-wk high 225.65; 23 analysts Buy avg 230.68. NOC (Northrop Grumman) at 571.58 - B-21 bomber, Sentinel ICBM, space; rev 42.9B, EPS 31.50, P/E 18.2, ROE 27%, backlog 105B, Golden Dome tailwind; 23 analysts Buy avg 643.28 (biggest implied upside of the three). Group counts after this batch: Computing Chips 8-&gt;9, Space 5-&gt;6, Drone &amp; Defence 4-&gt;8, Neocloud Watch 12-&gt;13, Power and Electrification 7-&gt;9.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C48"/>
+  <autoFilter ref="A1:C49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Pillar4_Stock_Notes.xlsx
+++ b/Pillar4_Stock_Notes.xlsx
@@ -16,10 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Follow-ups" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Index'!$A$1:$M$147</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$274</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock Index'!$A$1:$M$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comment Log'!$A$1:$D$281</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Full Log'!$A$1:$D$1473</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Dashboard Notes'!$A$1:$C$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Our Notes'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Follow-ups'!$A$1:$D$20</definedName>
   </definedNames>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6432,12 +6432,12 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>SoundHound AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -6450,7 +6450,7 @@
       <c r="F110" s="8" t="n"/>
       <c r="G110" s="9" t="n"/>
       <c r="H110" s="9" t="n">
-        <v>8.02</v>
+        <v>362.5</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -6463,42 +6463,52 @@
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Fintech / Digital Platform</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-      <c r="G111" s="9" t="n"/>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>3914.12</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H111" s="9" t="n">
-        <v>362.5</v>
+        <v>214.42</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
@@ -6511,29 +6521,29 @@
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>All 13 sets are in — but I caught a data problem: the agents returned enterprise value in $B instead of the EV/EBITDA ratio for every name (e.g. Visa "680" = its ~$670B EV, not a 28× multiple). P/FCF and everything else checks out. Let me send the three agents back to fetch the correct EV/EBITDA multiples before I write anything.</t>
+          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -6541,22 +6551,12 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F112" s="8" t="n">
-        <v>3914.12</v>
-      </c>
-      <c r="G112" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D112" s="11" t="inlineStr"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="8" t="n"/>
+      <c r="G112" s="9" t="n"/>
       <c r="H112" s="9" t="n">
-        <v>214.42</v>
+        <v>159.64</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
@@ -6569,29 +6569,29 @@
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>How cost and market value both show up. The reference poster only shows one number per company. Yours shows two, like this: the *width* of each slice is how much of the portfolio that stock is worth today, and the coloured band on the outside rim is your profit or loss on it. Gold band = profit, red band = loss, and the deeper the band, the bigger the move. Think of each slice as a glass of water: the whole glass is what it's worth now, and the coloured layer at the top is the part that's pure gain (or, in red, how far underwater you are). AMAT and CRWD have fat gold rims because they've roughly doubled; META, TSLA and IBM show red.</t>
+          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -6604,7 +6604,7 @@
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="9" t="n"/>
       <c r="H113" s="9" t="n">
-        <v>159.64</v>
+        <v>300.27</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -6627,19 +6627,19 @@
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>One honest note on Fortinet, since Dad has it on the list at under $100: it reported a strong quarter on July 29 — revenue $2.05B up 26%, billings up 33%, earnings up 41%, and it raised full-year guidance. That's why it's near its 52-week high at $168 rather than anywhere near $100. Dad's number on that one looks anchored to a price from a long time ago.</t>
+          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -6647,12 +6647,22 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr"/>
-      <c r="E114" s="7" t="n"/>
-      <c r="F114" s="8" t="n"/>
-      <c r="G114" s="9" t="n"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>3760.62</v>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H114" s="9" t="n">
-        <v>300.27</v>
+        <v>363.86</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -6665,29 +6675,29 @@
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>NET was a move, not an addition. Each stock can only sit in one group on the dashboard, so putting Cloudflare into SaaS took it out of Cybersecurity. Cybersecurity now has four names instead of five. If you'd rather it stayed in Cybersecurity, say the word and I'll put it back.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RBRK</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -6695,26 +6705,16 @@
           <t>Cybersecurity</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="F115" s="8" t="n">
-        <v>3760.62</v>
-      </c>
-      <c r="G115" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D115" s="11" t="inlineStr"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="8" t="n"/>
+      <c r="G115" s="9" t="n"/>
       <c r="H115" s="9" t="n">
-        <v>363.86</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J115" s="5">
@@ -6723,29 +6723,29 @@
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>RBRK</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -6758,11 +6758,11 @@
       <c r="F116" s="8" t="n"/>
       <c r="G116" s="9" t="n"/>
       <c r="H116" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>168.68</v>
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J116" s="5">
@@ -6771,42 +6771,52 @@
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="8" t="n"/>
-      <c r="G117" s="9" t="n"/>
+          <t>Nuclear Energy</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>1994.06</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>5000</v>
+      </c>
       <c r="H117" s="9" t="n">
-        <v>168.68</v>
+        <v>169.9</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -6819,29 +6829,29 @@
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>The group tells a clean story now that it's isolated: FTNT and PANW are the profitable, cash-generating incumbents; CRWD and ZS are the scaled-but-barely-profitable platform players; NET is the expensive hyper-growth bet. Having them side by side makes the valuation spread obvious — you're paying 32× forward for Zscaler and 200× for Cloudflare for similar ~25-34% growth, which is exactly the kind of relative-value comparison the grouping should surface.</t>
+          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Cameco</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -6849,22 +6859,12 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F118" s="8" t="n">
-        <v>1994.06</v>
-      </c>
-      <c r="G118" s="9" t="n">
-        <v>5000</v>
-      </c>
+      <c r="D118" s="11" t="inlineStr"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="9" t="n"/>
       <c r="H118" s="9" t="n">
-        <v>169.9</v>
+        <v>97.39</v>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
@@ -6877,29 +6877,29 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>One housekeeping flag on my own sources: CNN's quote pages gave me clearly wrong numbers this morning (Centrus at $331 versus the correct $184.76, BWXT at $205 versus $173.79). I discarded them and used stockanalysis.com, cross-checked against Google Finance and dated news reports. I mention it only so you know I checked rather than trusted.</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Cameco</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -6907,12 +6907,22 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr"/>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="8" t="n"/>
-      <c r="G119" s="9" t="n"/>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>4040.98</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H119" s="9" t="n">
-        <v>97.39</v>
+        <v>269.89</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -6925,29 +6935,29 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -6955,22 +6965,12 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F120" s="8" t="n">
-        <v>4040.98</v>
-      </c>
-      <c r="G120" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D120" s="11" t="inlineStr"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="8" t="n"/>
+      <c r="G120" s="9" t="n"/>
       <c r="H120" s="9" t="n">
-        <v>269.89</v>
+        <v>191.37</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
@@ -6981,31 +6981,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A120)</f>
         <v/>
       </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K120" s="5" t="inlineStr"/>
+      <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>Nano Nuclear Energy</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -7018,7 +7010,7 @@
       <c r="F121" s="8" t="n"/>
       <c r="G121" s="9" t="n"/>
       <c r="H121" s="9" t="n">
-        <v>191.37</v>
+        <v>18.85</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
@@ -7029,23 +7021,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A121)</f>
         <v/>
       </c>
-      <c r="K121" s="5" t="inlineStr"/>
-      <c r="L121" s="5" t="inlineStr"/>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Nano Nuclear Energy</t>
+          <t>Oklo</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -7058,7 +7058,7 @@
       <c r="F122" s="8" t="n"/>
       <c r="G122" s="9" t="n"/>
       <c r="H122" s="9" t="n">
-        <v>18.85</v>
+        <v>48.42</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -7071,29 +7071,29 @@
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>One gap: NNE has no reliable 52-week low. It's printing fresh lows almost daily and I got six conflicting candidates (14.71 / 14.78 / 14.89 / 15.44 / 15.78 / 18.04). It renders "range n/a" with no band. Your call whether to leave it null or pin the lowest evidenced print with a flag.</t>
+          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Oklo</t>
+          <t>NuScale Power</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -7106,7 +7106,7 @@
       <c r="F123" s="8" t="n"/>
       <c r="G123" s="9" t="n"/>
       <c r="H123" s="9" t="n">
-        <v>48.42</v>
+        <v>9.82</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
@@ -7119,29 +7119,29 @@
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>The list appears to have shrunk between Jul 28 and Jul 30. Commit `de9db26` (the Jul 28 refresh) successfully updated 58 tickers including ARM, AEHR, SKHY, CRWV, NBIS, OKLO, SMCI, SNDK, WDC, MDB, NOW, NET, ZS, MELI, SE, NU — every one of which returns ACCESS DENIED now. Commit `680b95b` on Jul 30 got exactly the 23.</t>
+          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>UUUU</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>NuScale Power</t>
+          <t>Energy Fuels</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -7154,42 +7154,34 @@
       <c r="F124" s="8" t="n"/>
       <c r="G124" s="9" t="n"/>
       <c r="H124" s="9" t="n">
-        <v>9.82</v>
+        <v>12.9</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J124" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A124)</f>
         <v/>
       </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K124" s="5" t="inlineStr"/>
+      <c r="L124" s="5" t="inlineStr"/>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>⚠️ Read these as the same *type* of bet you already hold in IREN/NBIS/CRWV — pre-profit infrastructure plays, not businesses with an earnings floor. All three lose money, all three have blank P/E, EV/EBITDA, and P/FCF on the dashboard because there's no positive earnings or EBITDA yet, and all three show large *negative* free cash flow. Same caveat I gave you on the neobanks and NuScale: that negative FCF is datacenter capex — they're spending billions to build GPU/HPC capacity ahead of revenue. Whether that's brilliant or reckless depends entirely on whether the AI-hosting contracts show up to fill it. I nulled the Rule-of-40 on APLD and CIFR because capex swamps it into meaningless −450% territory; only HUT (71.5) is computable.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>UUUU</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Energy Fuels</t>
+          <t>Vistra</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -7197,39 +7189,57 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="8" t="n"/>
-      <c r="G125" s="9" t="n"/>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>6078.05</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H125" s="9" t="n">
-        <v>12.9</v>
+        <v>140.67</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J125" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A125)</f>
         <v/>
       </c>
-      <c r="K125" s="5" t="inlineStr"/>
-      <c r="L125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>XE</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Vistra</t>
+          <t>X-energy (IPO Apr 24 '26)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -7237,26 +7247,16 @@
           <t>Nuclear Energy</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="F126" s="8" t="n">
-        <v>6078.05</v>
-      </c>
-      <c r="G126" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D126" s="11" t="inlineStr"/>
+      <c r="E126" s="7" t="n"/>
+      <c r="F126" s="8" t="n"/>
+      <c r="G126" s="9" t="n"/>
       <c r="H126" s="9" t="n">
-        <v>140.67</v>
+        <v>20.82</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J126" s="5">
@@ -7265,46 +7265,56 @@
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>Three — two of your existing holdings report this week. Constellation (CEG) reports tomorrow, Aug 6, and Vistra (VST) reports Friday, Aug 7. You own both. Wait and see those before adding anything else to the power/energy side. CEG also declared a dividend of $0.4265 per share this morning.</t>
+          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>XE</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>X-energy (IPO Apr 24 '26)</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Nuclear Energy</t>
-        </is>
-      </c>
-      <c r="D127" s="11" t="inlineStr"/>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="8" t="n"/>
-      <c r="G127" s="9" t="n"/>
+          <t>Power and Electrification</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>7879.55</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H127" s="9" t="n">
-        <v>20.82</v>
+        <v>448.68</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J127" s="5">
@@ -7313,29 +7323,29 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>Two stocks are still showing Monday's price: XE (X-Energy) and YUM. Every free source I tried served me either a stale snapshot or a mid-day price with no closing print. Rather than put a number on the dashboard I couldn't stand behind, I left both at their Aug 3 close and said so in the dashboard's own header. They're watchlist names, so nothing you own is affected.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
@@ -7349,16 +7359,16 @@
         </is>
       </c>
       <c r="E128" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>7879.55</v>
+        <v>2147.3</v>
       </c>
       <c r="G128" s="9" t="n">
         <v>10000</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>448.68</v>
+        <v>990.3200000000001</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -7371,29 +7381,29 @@
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Hubbell</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
@@ -7401,22 +7411,12 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F129" s="8" t="n">
-        <v>2147.3</v>
-      </c>
-      <c r="G129" s="9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D129" s="11" t="inlineStr"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="8" t="n"/>
+      <c r="G129" s="9" t="n"/>
       <c r="H129" s="9" t="n">
-        <v>990.3200000000001</v>
+        <v>513.99</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
@@ -7429,29 +7429,29 @@
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>HYLN</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Hubbell</t>
+          <t>Hyliion Holdings</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
@@ -7464,7 +7464,7 @@
       <c r="F130" s="8" t="n"/>
       <c r="G130" s="9" t="n"/>
       <c r="H130" s="9" t="n">
-        <v>513.99</v>
+        <v>3.87</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -7475,31 +7475,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A130)</f>
         <v/>
       </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K130" s="5" t="inlineStr"/>
+      <c r="L130" s="5" t="inlineStr"/>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>HYLN</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Hyliion Holdings</t>
+          <t>Monolithic Power</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
@@ -7507,12 +7499,22 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr"/>
-      <c r="E131" s="7" t="n"/>
-      <c r="F131" s="8" t="n"/>
-      <c r="G131" s="9" t="n"/>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>1538.56</v>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>5000</v>
+      </c>
       <c r="H131" s="9" t="n">
-        <v>3.87</v>
+        <v>1401.54</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -7523,23 +7525,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A131)</f>
         <v/>
       </c>
-      <c r="K131" s="5" t="inlineStr"/>
-      <c r="L131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Monolithic Power</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -7547,22 +7557,12 @@
           <t>Power and Electrification</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="8" t="n">
-        <v>1538.56</v>
-      </c>
-      <c r="G132" s="9" t="n">
-        <v>5000</v>
-      </c>
+      <c r="D132" s="11" t="inlineStr"/>
+      <c r="E132" s="7" t="n"/>
+      <c r="F132" s="8" t="n"/>
+      <c r="G132" s="9" t="n"/>
       <c r="H132" s="9" t="n">
-        <v>1401.54</v>
+        <v>164.69</v>
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
@@ -7575,29 +7575,29 @@
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>The picture got further away, not closer. Amazon jumped 15% and Monolithic Power 10.6% overnight — both blew straight through your limits. Google added 4.6%. Nothing moved toward you except Micron and Coinbase, and both are still short of the mark. ISRG remains the nearest at 5.6%, and it's drifting your way rather than away.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>POWI</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>Power Integrations</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
@@ -7610,7 +7610,7 @@
       <c r="F133" s="8" t="n"/>
       <c r="G133" s="9" t="n"/>
       <c r="H133" s="9" t="n">
-        <v>164.69</v>
+        <v>64.59</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -7621,31 +7621,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A133)</f>
         <v/>
       </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="K133" s="5" t="inlineStr"/>
+      <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>POWI</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Power Integrations</t>
+          <t>Powell Industries</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -7658,7 +7650,7 @@
       <c r="F134" s="8" t="n"/>
       <c r="G134" s="9" t="n"/>
       <c r="H134" s="9" t="n">
-        <v>64.59</v>
+        <v>211.56</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -7669,23 +7661,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A134)</f>
         <v/>
       </c>
-      <c r="K134" s="5" t="inlineStr"/>
-      <c r="L134" s="5" t="inlineStr"/>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>POWL</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Powell Industries</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
@@ -7698,7 +7698,7 @@
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="9" t="n"/>
       <c r="H135" s="9" t="n">
-        <v>211.56</v>
+        <v>671.86</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -7721,24 +7721,24 @@
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>Three honest data caveats. Rubrik's closing price disagreed with itself on the same website — $80.99 on two pages versus $79.64 on a third. I used $80.99 because Google Finance agrees and it matches the reported +8.36% move exactly. nVent had the same problem ($162.24 vs $163.68); same resolution, two sources to one. And Powell's "return on invested capital" showed an implausible 122.6% on one page against 38.4% and ~32% elsewhere — I stored the conservative 38.4% rather than the flattering number.</t>
+          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>AIRJ</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>AirJoule Technologies</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Power and Electrification</t>
+          <t>Renewal Energy</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr"/>
@@ -7746,7 +7746,7 @@
       <c r="F136" s="8" t="n"/>
       <c r="G136" s="9" t="n"/>
       <c r="H136" s="9" t="n">
-        <v>671.86</v>
+        <v>5.92</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -7764,24 +7764,24 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>The new group "Power and Electrification" now exists with all six names. Two of them are things you already own: ETN (19 shares, $7,879.55 cost) and GEV (2 shares, $2,147.30 cost). They moved out of Energy, so Energy shrinks from 13 names to 11 and the new group starts with real money in it rather than being an empty watchlist. Your total cost and market value are unchanged to the cent ($560,431.70 / $683,857.21) — nothing was bought or sold, the money just sits under a different heading now. PWR, POWL, NVT and HUBB are watchlist only.</t>
+          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>AIRJ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>AirJoule Technologies</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
@@ -7794,7 +7794,7 @@
       <c r="F137" s="8" t="n"/>
       <c r="G137" s="9" t="n"/>
       <c r="H137" s="9" t="n">
-        <v>5.92</v>
+        <v>219.34</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -7805,31 +7805,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A137)</f>
         <v/>
       </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="L137" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
+      <c r="K137" s="5" t="inlineStr"/>
+      <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>I want to be fair to it, because it's the most interesting of the three rejects. AirJoule has a 50/50 joint venture with GE Vernova that is genuinely operating — they installed a unit at GE Vernova's research campus in New York on July 28. Kubota signed them as exclusive US residential partner on July 21 (the stock jumped 15% that day). They have $35M cash and no debt, funded into 2028. All five analysts covering it have targets above the current price — the lowest target, $6.00, sits above the $5.95 price.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Fluence Energy</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
@@ -7842,7 +7834,7 @@
       <c r="F138" s="8" t="n"/>
       <c r="G138" s="9" t="n"/>
       <c r="H138" s="9" t="n">
-        <v>219.34</v>
+        <v>13.2</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -7853,23 +7845,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A138)</f>
         <v/>
       </c>
-      <c r="K138" s="5" t="inlineStr"/>
-      <c r="L138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Fluence Energy</t>
+          <t>MYR Group</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="F139" s="8" t="n"/>
       <c r="G139" s="9" t="n"/>
       <c r="H139" s="9" t="n">
-        <v>13.2</v>
+        <v>337.42</v>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
@@ -7893,31 +7893,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A139)</f>
         <v/>
       </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
+      <c r="K139" s="5" t="inlineStr"/>
+      <c r="L139" s="5" t="inlineStr"/>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>APP, FLNC and MELI fell because their numbers got worse. When analysts update, they will cut their forecasts, and the stock has further to adjust downward.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>MYR Group</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
@@ -7930,7 +7922,7 @@
       <c r="F140" s="8" t="n"/>
       <c r="G140" s="9" t="n"/>
       <c r="H140" s="9" t="n">
-        <v>337.42</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -7941,23 +7933,31 @@
         <f>COUNTIF('Full Log'!$A:$A,$A140)</f>
         <v/>
       </c>
-      <c r="K140" s="5" t="inlineStr"/>
-      <c r="L140" s="5" t="inlineStr"/>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>No comment on record yet.</t>
+          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
@@ -7970,7 +7970,7 @@
       <c r="F141" s="8" t="n"/>
       <c r="G141" s="9" t="n"/>
       <c r="H141" s="9" t="n">
-        <v>84.65000000000001</v>
+        <v>118.13</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -7983,29 +7983,29 @@
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
-          <t>&gt; If you're deploying real capital into this group: CCJ or NEE for conviction, the five SMR/storage names only as small, sized-to-lose speculative positions. I'd resist the temptation to treat OKLO/SMR at −75%/−83% as "cheap" — down a lot isn't the same as cheap when there's no earnings floor underneath.</t>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Vertiv Holdings</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
@@ -8013,12 +8013,22 @@
           <t>Renewal Energy</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr"/>
-      <c r="E142" s="7" t="n"/>
-      <c r="F142" s="8" t="n"/>
-      <c r="G142" s="9" t="n"/>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F142" s="8" t="n">
+        <v>3524.44</v>
+      </c>
+      <c r="G142" s="9" t="n">
+        <v>10000</v>
+      </c>
       <c r="H142" s="9" t="n">
-        <v>118.13</v>
+        <v>272.4</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -8031,56 +8041,46 @@
       </c>
       <c r="K142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
-          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+          <t>Strategically it is also the cleanest fit for what you already own. APH is the interconnect layer — every AI rack you have exposure to through NVDA, AVGO, VRT, ANET and CRDO needs Amphenol's connectors and cable assemblies. It is the pick-and-shovel play on your own book, and it is your smallest deployed position relative to budget.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Vertiv Holdings</t>
+          <t>Affirm Holdings</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Renewal Energy</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F143" s="8" t="n">
-        <v>3524.44</v>
-      </c>
-      <c r="G143" s="9" t="n">
-        <v>10000</v>
-      </c>
+          <t>Digital Applications</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr"/>
+      <c r="E143" s="7" t="n"/>
+      <c r="F143" s="8" t="n"/>
+      <c r="G143" s="9" t="n"/>
       <c r="H143" s="9" t="n">
-        <v>272.4</v>
+        <v>79.56</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="J143" s="5">
@@ -8089,29 +8089,29 @@
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
-          <t>Strategically it is also the cleanest fit for what you already own. APH is the interconnect layer — every AI rack you have exposure to through NVDA, AVGO, VRT, ANET and CRDO needs Amphenol's connectors and cable assemblies. It is the pick-and-shovel play on your own book, and it is your smallest deployed position relative to budget.</t>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Affirm Holdings</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
@@ -8124,30 +8124,22 @@
       <c r="F144" s="8" t="n"/>
       <c r="G144" s="9" t="n"/>
       <c r="H144" s="9" t="n">
-        <v>79.56</v>
+        <v>214.42</v>
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J144" s="5">
         <f>COUNTIF('Full Log'!$A:$A,$A144)</f>
         <v/>
       </c>
-      <c r="K144" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L144" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K144" s="5" t="inlineStr"/>
+      <c r="L144" s="5" t="inlineStr"/>
       <c r="M144" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8194,12 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
@@ -8220,7 +8212,7 @@
       <c r="F146" s="8" t="n"/>
       <c r="G146" s="9" t="n"/>
       <c r="H146" s="9" t="n">
-        <v>151.57</v>
+        <v>74.14</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -8231,31 +8223,23 @@
         <f>COUNTIF('Full Log'!$A:$A,$A146)</f>
         <v/>
       </c>
-      <c r="K146" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
+      <c r="K146" s="5" t="inlineStr"/>
+      <c r="L146" s="5" t="inlineStr"/>
       <c r="M146" s="10" t="inlineStr">
         <is>
-          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+          <t>No comment on record yet.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Uber Technologies</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
@@ -8268,7 +8252,7 @@
       <c r="F147" s="8" t="n"/>
       <c r="G147" s="9" t="n"/>
       <c r="H147" s="9" t="n">
-        <v>75.02</v>
+        <v>151.57</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -8281,22 +8265,318 @@
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>&gt; The through-line: this group splits cleanly into two things you already own the framework for — V/MA/PYPL are your "quality + value" wheelhouse (toll-road economics, the exact income-and-value lens you use on Thai equity), while COIN/HOOD/AFRM/SHOP are momentum-and-story names where valuation still has a long way to fall if growth blinks. Don't let them sit in one mental bucket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>SoundHound AI</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Digital Applications</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr"/>
+      <c r="E148" s="7" t="n"/>
+      <c r="F148" s="8" t="n"/>
+      <c r="G148" s="9" t="n"/>
+      <c r="H148" s="9" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J148" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A148)</f>
+        <v/>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 PM stamp; the Aug 5 close was 120.73 (cleanly sourced) and Aug 7 opened ~119 and traded up ~2% - treat 119.05 as the Aug 6 close, tonight's refresh will confirm. NRG is a big Texas integrated power company: independent power generation + retail electricity + home services, now heavily positioned around DATA-CENTRE / AI power demand (Q2 earnings call flagged a landmark 1.2GW - expandable to 2.4GW - 'bring your own power' deal with a hyperscaler in ERCOT, ~500M annual EBITDA at full run, COD ~late 2029). GAAP-profitable and pays a dividend (~1.57% yield, 1.90/yr): revenue 33.13B TTM (+12.8%), ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Uber Technologies</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Digital Applications</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr"/>
+      <c r="E149" s="7" t="n"/>
+      <c r="F149" s="8" t="n"/>
+      <c r="G149" s="9" t="n"/>
+      <c r="H149" s="9" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J149" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A149)</f>
+        <v/>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="L147" s="5" t="inlineStr">
+      <c r="L149" s="5" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="M147" s="10" t="inlineStr">
+      <c r="M149" s="10" t="inlineStr">
         <is>
           <t>This is the discipline point. Uber is a sophisticated technology company that deployed AI aggressively across its organisation and, by its own admission, cannot yet prove it paid for itself. "This company uses AI" is not a thesis. "AI attacks a cost line that is large, and compounds on data nobody else has" — that's a thesis.</t>
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Digital Applications</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr"/>
+      <c r="E150" s="7" t="n"/>
+      <c r="F150" s="8" t="n"/>
+      <c r="G150" s="9" t="n"/>
+      <c r="H150" s="9" t="n">
+        <v>179.64</v>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J150" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A150)</f>
+        <v/>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
+      <c r="L150" s="5" t="inlineStr"/>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>No comment on record yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Industrial STX</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr"/>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="8" t="n"/>
+      <c r="G151" s="9" t="n"/>
+      <c r="H151" s="9" t="n">
+        <v>842.1900000000001</v>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J151" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A151)</f>
+        <v/>
+      </c>
+      <c r="K151" s="5" t="inlineStr"/>
+      <c r="L151" s="5" t="inlineStr"/>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>No comment on record yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Deere &amp; Co</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Industrial STX</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr"/>
+      <c r="E152" s="7" t="n"/>
+      <c r="F152" s="8" t="n"/>
+      <c r="G152" s="9" t="n"/>
+      <c r="H152" s="9" t="n">
+        <v>620.83</v>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J152" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A152)</f>
+        <v/>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
+      <c r="L152" s="5" t="inlineStr"/>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>No comment on record yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Industrial STX</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr"/>
+      <c r="E153" s="7" t="n"/>
+      <c r="F153" s="8" t="n"/>
+      <c r="G153" s="9" t="n"/>
+      <c r="H153" s="9" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J153" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A153)</f>
+        <v/>
+      </c>
+      <c r="K153" s="5" t="inlineStr"/>
+      <c r="L153" s="5" t="inlineStr"/>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>No comment on record yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>3M Co</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Industrial STX</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr"/>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="8" t="n"/>
+      <c r="G154" s="9" t="n"/>
+      <c r="H154" s="9" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J154" s="5">
+        <f>COUNTIF('Full Log'!$A:$A,$A154)</f>
+        <v/>
+      </c>
+      <c r="K154" s="5" t="inlineStr"/>
+      <c r="L154" s="5" t="inlineStr"/>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>No comment on record yet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8307,7 +8587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17695,20 +17975,2405 @@
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C217" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C218" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D218" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The July 4-for-1 CRWD split was never applied to the manual record: the sheet showed CrowdStrike as the second-worst loser at -51% when it is actually up about +95%.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Fix is one row: 40 shares at $97.98 average cost, which ties the sheet to the broker to the dollar; the dashboard had already split-adjusted CRWD.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ CRWD is up +108%, helping make Software (+56%) one of the best-performing groups.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  A new Cybersecurity group was created: CRWD moved there with PANW, ZS, NET and FTNT — CRWD and ZS read as scaled but barely profitable platform players.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Minor drift: trimming $5.00 of commission from the CRWD cost row is part of a $254 fix to make the sheet match the broker to the cent.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  FTNT added to the board with ZS and NET, then moved into a new 16-name-era Cybersecurity group alongside CRWD, PANW, ZS and NET.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ It is the group's quality anchor - the only profitable one: 27% net margin, 132% ROE, 80% gross margin, $2.4B of real free cash flow; at 49x forward not cheap, but a cash machine.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C221" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D221" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C222" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D222" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Verdict: skip. After doubling this year (+104%), the average analyst target of $131.78 sits 19% BELOW the $161.95 price, and it trades at 49x forward earnings.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ The business is strong: Jul 29 quarter had revenue $2.05B up 26%, billings up 33%, earnings up 41%, and raised full-year guidance - hence the stock near its high at $168.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Dad's limits are far away: his $130 limit is near the Street's fair value but 25% below market; his sub-$100 limit is 40.6% below - anchored to an old price; nothing triggered.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C223" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Cloudflare flagged as the single most expensive name in the ~100-stock book: 202x forward P/E, ~860x EV/EBITDA, ~40x sales - priced for flawless execution.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Fastest grower in the cyber group at +34%, expanding into AI-inference at the edge - but a momentum bet, not a value one.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved with CRWD, PANW, ZS and FTNT into a new dedicated Cybersecurity group, making the valuation spread across the five obvious.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C224" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D224" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B225" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C225" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D225" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  PANW, first filed under Chips Manufacturing per the handwritten note, moved into a new Cybersecurity group with CRWD, ZS, NET and FTNT.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Within the cyber group, FTNT and PANW stand out as the profitable, cash-generating incumbents versus 32x-200x forward growth peers with similar ~25-34% growth.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C226" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D226" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  RBRK (Rubrik) added to the Cybersecurity group at $80.99 - watchlist only, no money in it.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Jumped 8.4% on Aug 4 when Loop Capital initiated coverage with a Buy and a $100 target.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Still loses money and has negative shareholder equity, so its ROE and debt ratios are shown blank.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Price sources conflicted ($80.99 vs $79.64); $80.99 was used since Google Finance agrees and it matches the reported +8.36% move exactly.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="B227" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D227" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ZS added to the board (tipping it to 100 tickers), then moved into the new Cybersecurity group with CRWD, PANW, NET and FTNT.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ ZS is the more reasonable entry of the unprofitable cyber names: best Rule of 40 (56), $960M FCF-positive at breakeven, and already down 58% from its high.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  The group makes the valuation spread obvious: ~32x forward for Zscaler vs ~200x for Cloudflare at similar 25-34% growth.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>BWXT</t>
+        </is>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C228" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D228" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  BWXT's Aug 3 after-market earnings were picked up by the overnight refresh and merged cleanly - all dashboard checks passed (110 stocks, 47 held, totals unchanged).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  BWXT is crossed out on Dad's note, so it was treated as cancelled and excluded from the buy recommendation.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: CNN quoted BWXT at $205 vs the correct $173.79; the bad source was discarded and prices cross-checked via stockanalysis.com and Google Finance.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C229" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Called the cleanest way to play the nuclear buildout without SMR execution risk: actual uranium, actual profit, +113% EPS growth, ~50% analyst upside (avg target $131).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Not cheap at 60x forward earnings.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Named alongside NEE as the conviction picks for real capital in the energy group; SMR/storage names only as small, sized-to-lose speculation.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>CCJ</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C230" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D230" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B231" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C231" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D231" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  CEG reports earnings Aug 6 (VST, also held, reports Aug 7); advice is to wait for both prints before adding anything on the power/energy side.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ CEG declared a dividend of $0.4265 per share on the morning of Aug 5.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Keep about $5,150 in reserve so a post-earnings selloff in CEG or VST can be bought.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>LEU</t>
+        </is>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C232" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D232" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  LEU (Centrus Energy) added to Nuclear Energy at the Aug 7 close $191.37. The only US-owned uranium ENRICHER - makes HALEU fuel for next-gen/small reactors. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Profitable and strategically vital: revenue $474M, 10% net margin, a $4.5B order backlog through 2040, a $900M US government HALEU award, and $1.87B cash.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Expensive and volatile: 88x earnings, negative free cash flow (heavy plant spending), 26% of shares sold short, and it swings hugely - 52-week range $142 to $464. Dropped 5% on earnings then bounced 7% next day.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="B233" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D234" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  OKLO added to the Energy group as a watchlist name among eight energy additions (SMRs, uranium, solar/storage, a utility), with ~$40K reserved for Energy buys.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Warning: OKLO is one of five names with essentially no profits and little revenue - valuation columns are blank; treat as a thematic call option and size it like a venture bet.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Do not read OKLO at -75% off its high as cheap - down a lot is not cheap with no earnings floor; only small, sized-to-lose speculation (CCJ or NEE for conviction instead).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="inlineStr">
+        <is>
+          <t>OKLO</t>
+        </is>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C236" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D236" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t>SMR</t>
+        </is>
+      </c>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- SMR is one of five energy names (with OKLO, NNE, TE, EOSE) with essentially no profits — valuation columns blank; thematic call options to be sized like venture bets.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Warning: do not read OKLO/SMR at -75%/-83% off highs as cheap — down a lot is not the same as cheap when there is no earnings floor underneath.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  For real capital in the group, CCJ or NEE were preferred; the SMR-type names only as small, sized-to-lose speculative positions.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>UUUU</t>
+        </is>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C238" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D238" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  UUUU (Energy Fuels) added to Nuclear Energy at the Aug 6 close $12.90 (rebounded ~10% Aug 7). A US uranium miner that also processes rare-earth elements at its Utah mill. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Strong balance sheet: ~$996M working capital (cash + marketable securities), producing real uranium (865k lbs last quarter, sold at $80/lb) and building a rare-earths plant.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Loses money today: -77% net margin, EPS -$0.34, burning ~$120M cash a year. No P/E - you're buying the uranium/rare-earth theme, not profits. 20% of shares are sold short.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D240" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- VST fell 8.15% to $143.23 - the worst day among the holdings; the drop was confirmed by POEMS and Google Finance against one source claiming $145.46.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VST reports Friday Aug 7 (CEG Aug 6); advice: keep ~$5,150 in reserve and wait for both prints before adding on the power/energy side.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VST moved from Energy to Nuclear Energy group (we own 42 sh, cost $6,078, budget $10,000) - its P&amp;L now reports under Nuclear Energy.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 changes: AXON (Axon Enterprise, NASDAQ - Tasers, body cameras, drones/counter-drone and evidence software for public safety) added to Drone &amp; Defense at the Aug 6, 2026 close 522.46, DOWN 14.28% on the day, header stamped "At close: Aug 6, 2026, 4:00 PM EDT" and confirmed by MarketBeat; note ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>XE</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C241" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  XE (X-Energy) deliberately left at Monday's Aug 3 close - no trustworthy fresh close was available; the staleness is disclosed on the dashboard; watchlist only, no position.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy to Nuclear Energy (X-energy is a nuclear/small-reactor developer, so it belongs there). Group label only.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C242" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D242" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B243" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C243" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The $300 buy limit sits below Eaton's 52-week low of $311.92 - it waits for ground untouched in a year; analyst average is $455.79, 52% above the desired entry.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Checksum caught a transcription error: ETN was keyed 386.20 vs actual 386.26; fixed, and earnings-related fundamentals refresh on ETN preserved.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C244" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D244" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B245" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C245" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D246" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  GEV (2 shares, $2,147.30 cost) moved with ETN into a new Power and Electrification group; totals unchanged to the cent, nothing bought or sold.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- GE Vernova JV partner AirJoule: genuinely operating (unit installed Jul 28, Kubota deal Jul 21) but no revenue, 16 employees and a $46M funding hole - a ticket, not a position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="inlineStr">
+        <is>
+          <t>HUBB</t>
+        </is>
+      </c>
+      <c r="B247" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C247" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Hubbell was pulled fresh onto the dashboard and joined the new Power &amp; Electrification group as a watchlist name at $502.24.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ It beat and raised on grid modernization and data centres - the steadiest, lowest-volatility of the four new power names.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  None of Dad's nine buy limits are triggered; Hubbell is the closest, still 14.4% above his $430 line, with about +20% to the analyst target.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="inlineStr">
+        <is>
+          <t>HYLN</t>
+        </is>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C248" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D248" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  HYLN (Hyliion) added to Power &amp; Electrification at the Aug 7 close $3.87. Makes the KARNO generator - a fuel-flexible power module. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: Pre-revenue in practice: only $5.8M sales, so its price-to-sales (121x) is meaningless and it burns ~$64M/yr. Very volatile (beta 3.6). A bet on a technology, not a business yet.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Momentum from defence: won a $41.7M US Navy award to scale its power modules and demonstrated them running as one plant. $72M cash. 3 analysts Buy, avg $7. Q2 call Aug 12.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B249" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C249" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D249" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C250" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D250" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: Advisor admitted MPWR's 'live' price was filled in from memory, not retrieved; on a proper re-pull, four of five such prices were wrong.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Jumped 10.6% overnight, blowing straight through the standing buy limit - the entry moved further away.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Earnings-related fundamentals refresh on MPWR preserved during a data cleanup.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="B251" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C251" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D251" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Energy group cleaned up: MPWR now sits in a tighter 12-name electrification-and-power bucket with ETN, VRT, GEV, VST, NEE.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MPWR moved from Energy to Power &amp; Electrification group (we own 1 sh, cost $1,538.56, budget $5,000) - its P&amp;L now reports under Power &amp; Electrification. It makes power-management chips for AI/data-centre boards.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 move: MPWR (Monolithic Power Systems, HELD - 1 sh / 1,538.56 cost / 5,000 budget) moved Energy -&gt; Power and Electrification per request. Field values, position and budget untouched; group P&amp;L attribution now reports under Power and Electrification. Energy 11 -&gt; 10 names, Power and ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>NVT</t>
+        </is>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C252" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NVT (nVent Electric) added at $162.24 as watchlist-only in the new six-name Power and Electrification group (which also absorbed held positions ETN and GEV).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ nVent has raised full-year guidance twice on AI liquid-cooling demand and is buying back its own shares.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: sources disagreed on the close ($162.24 vs $163.68); $162.24 was stored on a two-sources-to-one basis.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
+        <is>
+          <t>POWI</t>
+        </is>
+      </c>
+      <c r="B253" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C253" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D253" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  POWI (Power Integrations) added to Power &amp; Electrification at the Aug 7 close $64.59. Makes energy-efficient power-conversion chips for industry, renewables and AI. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Rock-solid balance sheet (no debt, pays a dividend), 54% gross margins, and Q2 beat and jumped ~9%. A quality niche chipmaker levered to grid/renewables demand.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Barely profitable right now, so the P/E (147) and EV/EBITDA (80) look extreme; you're paying up for a recovery. Only 5 analysts, avg target $77. Stock $65 vs a $91 high.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>POWL</t>
+        </is>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C254" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Powell Industries missed on both revenue and profit Aug 3, gapping down almost 13% before closing -3.8%; with only four analysts covering it, the price moves violently.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ The order book tells the opposite story: new orders +158%, backlog +69%, and a 3.0x book-to-bill - three dollars booked for every dollar shipped.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Watchlist-only in the new Power &amp; Electrification group at $211.38; an implausible 122.6% return-on-capital figure was rejected for the conservative 38.4%.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="inlineStr">
+        <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="B255" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  PWR added watchlist-only to the new 'Power and Electrification' group alongside POWL, NVT and HUBB.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Quanta Services ($693) beat big on Jul 30 and raised full-year guidance - revenue +41%, backlog $53.4B; the stock jumped 13.65% that day.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>AIRJ</t>
+        </is>
+      </c>
+      <c r="B256" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C256" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D256" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- AIRJ is filed under Energy but is really an industrial equipment maker (atmospheric water capture); a lottery ticket, and its news is about drinking water, not energy.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Real traction: 50/50 JV with GE Vernova is operating (unit installed at GE's NY campus Jul 28); Kubota signed as exclusive US residential partner Jul 21, stock +15% that day.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Balance sheet is clean: $35M cash, no debt, funded into 2028; all five covering analysts have targets above the price (lowest $6.00 vs $5.95).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- But there is no revenue at all - advisor's verdict: interesting, not a buy today.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Data caveat: the $5.84 Aug 4 close comes from a single source; no second source had that day's data.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Housekeeping: AIRJ was already in Energy, so the regrouping request needed no action.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B257" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C257" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D257" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>FLNC</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">RED FLAG: FLNC missed Q3 badly on Aug 5: revenue $649.8M vs $806.2M expected (-19.4%), EPS -$0.24 vs +$0.02, full-year guidance cut to $2.9-3.1B from $3.2-3.6B; shares fell to ~$10.89.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Verdict: a falling knife — do not buy; analysts will cut forecasts and the stock likely has further to fall.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- The $14.23 stored on the dashboard is the pre-release close and is stale; sources also disagree on FLNC's market cap ($1.43B-$2.62B), EPS, ROE and net margin.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  FLNC had just been added to the Energy group at the Aug 5 close of $14.23 before the report; the next refresh will capture the gap down.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
+        <is>
+          <t>MYRG</t>
+        </is>
+      </c>
+      <c r="B259" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C259" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D259" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MYRG (MYR Group - you wrote 'MYR') added to the new Renewal Energy group at the Aug 7 close $337.42. An electrical-infrastructure builder: power lines, substations and data-centre/grid electrical work. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ High quality and profitable: revenue $4B (+16%), earnings more than doubled to $10.54/share, 25% return on capital, positive cash flow, almost no debt. Record Q2 and record $3.16B backlog.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Direct beneficiary of the grid buildout and data-centre electrification wave. Analysts see meaningful upside (avg ~$423 vs ~$337). Trades at a reasonable ~26x forward earnings for the growth.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- A contractor, so margins are thin (~4% net) and results can be lumpy project to project; the stock has pulled back from a $503 high.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C260" s="14" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="D260" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ NEE is the only dividend-quality name in the group: a $187B regulated utility plus the largest US renewables developer, 32% margins, near the ~$99 analyst fair value.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ For real capital in the nuclear/energy group: CCJ or NEE for conviction; the SMR and storage names only as small, sized-to-lose speculative bets.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B261" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C261" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NEE now sits in the cleaner electrification-and-power-equipment bucket (with ETN, VRT, GEV, VST, MPWR) after the Energy group was trimmed from 18 names to 12.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C262" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NRG (NRG Energy) added to Energy at the Aug 6 close $119.05. A big Texas power company - it generates electricity, sells it to homes, and is now a major play on data-centre/AI power demand. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Real, profitable business paying a ~1.6% dividend: $33B revenue, earnings up 76% to $3.87/share, 24% return on equity. Cheap on next year's earnings (~12x) with a bargain PEG of 0.5.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Growth catalyst: on its Aug 4 call it announced a landmark 1.2-gigawatt deal (expandable to 2.4GW) to power a hyperscaler's data centre in Texas - ~$500M/yr of profit once running, ~2029.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Heavily indebted (debt is ~5x equity - normal for a utility but real), and free cash flow is thin, so it looks expensive on a cash-flow basis (72x). Management sees this year's profit below the mid-point on soft Texas power prices.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Analysts still like it (~$194 avg target vs $119 now) but two firms trimmed targets on Aug 5; the stock touched a 52-week low ($112.50) recently. The $119.05 stored is the Aug 6 close - tonight's refresh confirms it.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B263" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C263" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- VRT reports earnings within a week - buying now means holding a binary event within days, which is why the week's buy pick went elsewhere.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Per-firm analyst rating actions for mid-caps like VRT need the FMP Starter plan (~$22-29/month); the upgrade was recommended as worthwhile.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C264" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="inlineStr">
+        <is>
+          <t>VRT</t>
+        </is>
+      </c>
+      <c r="B265" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C265" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D265" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  VRT now sits in the cleaner electrification-and-power-equipment bucket after the Energy group regrouping (18 names down to 12).
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C266" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D266" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Affirm screens at 19x forward earnings with +32% growth and a 10% margin; it has only just turned profitable and carries buy-now-pay-later credit risk.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Advisor files Affirm with the momentum-and-story names (Coinbase, Robinhood, Shopify), not the quality bucket - valuation has a long way to fall if growth blinks.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="B267" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C267" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D267" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C268" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  BKNG (Booking Holdings) added to Digital Applications at the Aug 7 close $214.42 (split-adjusted). The world's largest online travel agency (Booking.com, Priceline, Agoda). Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Exceptional economics: 87% gross margin, 92% return on invested capital, $9.5B cash flow; Q2 beat with profit up 131% and a record $3.7B buyback. 38 analysts Buy, avg ~$238.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Carries negative book equity from years of buybacks (so some ratios don't compute - normal for BKNG), and growth is moderating to high-single-digits.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="B269" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C269" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D269" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C270" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Verdict: parked, not rejected - it reported the night before, fell 4.5% with margins down 550bps; same timing trap as APP, revisit in a week once the dust settles.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Still the most attractive fundamentals of the candidate list: the cheapest cash flow of the lot at $1,922.57 with +15% upside shown and revenue growing 50%.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- Risk: MELI fell because its numbers got worse - when analysts update they will cut forecasts, so the stock likely has further to adjust downward.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="10" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B271" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C271" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  NFLX (Netflix) added to Digital Applications at the Aug 7 close $74.14 (price is low because of a 10-for-1 stock split in Nov 2025 - not comparable to old ~$700 levels). Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Elite business: 28% net margin, 49% return on equity, $11B free cash flow, trades at a reasonable 23x earnings. 51 analysts rate it Buy, avg target ~$94.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Down ~37% over the past year; Q2 earnings beat but weak next-quarter guidance knocked it ~9%. Growth is steady (low-teens), not explosive.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-20  (Jul 20-26, 2026)</t>
+        </is>
+      </c>
+      <c r="C272" s="12" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="D272" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="10" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="B273" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C273" s="13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="D273" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="inlineStr">
+        <is>
           <t>SOUN</t>
         </is>
       </c>
-      <c r="B217" s="10" t="inlineStr">
+      <c r="B274" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C217" s="13" t="inlineStr">
+      <c r="C274" s="13" t="inlineStr">
         <is>
           <t>MIXED</t>
         </is>
       </c>
-      <c r="D217" s="10" t="inlineStr">
+      <c r="D274" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17753,28 +20418,37 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
+            <t xml:space="preserve">  Moved into the Digital Applications group (from Fintech/Digital Platform). Group label only - no change to figures.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B218" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C218" s="13" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="10" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B275" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
+        </is>
+      </c>
+      <c r="C275" s="13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="D218" s="10" t="inlineStr">
+      <c r="D275" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17782,2319 +20456,28 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  Data fix: research agents returned Visa's ~$670B enterprise value instead of its EV/EBITDA multiple; they were sent back for correct multiples before anything was written.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="10" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B219" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C219" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D219" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The July 4-for-1 CRWD split was never applied to the manual record: the sheet showed CrowdStrike as the second-worst loser at -51% when it is actually up about +95%.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Fix is one row: 40 shares at $97.98 average cost, which ties the sheet to the broker to the dollar; the dashboard had already split-adjusted CRWD.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ CRWD is up +108%, helping make Software (+56%) one of the best-performing groups.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  A new Cybersecurity group was created: CRWD moved there with PANW, ZS, NET and FTNT — CRWD and ZS read as scaled but barely profitable platform players.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Minor drift: trimming $5.00 of commission from the CRWD cost row is part of a $254 fix to make the sheet match the broker to the cent.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="10" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="B220" s="10" t="inlineStr">
+            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B276" s="10" t="inlineStr">
         <is>
           <t>2026-08-03  (Aug 03-09, 2026)</t>
         </is>
       </c>
-      <c r="C220" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D220" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ On the new portfolio chart CRWD shows a fat gold profit rim — the position has roughly doubled.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B221" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C221" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D221" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  FTNT added to the board with ZS and NET, then moved into a new 16-name-era Cybersecurity group alongside CRWD, PANW, ZS and NET.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ It is the group's quality anchor - the only profitable one: 27% net margin, 132% ROE, 80% gross margin, $2.4B of real free cash flow; at 49x forward not cheap, but a cash machine.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B222" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C222" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D222" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: FTNT's quote-page close exceeded the history table's own daily high - proof the history table serves partial-day snapshots; the quote page has the real close.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="10" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="B223" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C223" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D223" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Verdict: skip. After doubling this year (+104%), the average analyst target of $131.78 sits 19% BELOW the $161.95 price, and it trades at 49x forward earnings.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ The business is strong: Jul 29 quarter had revenue $2.05B up 26%, billings up 33%, earnings up 41%, and raised full-year guidance - hence the stock near its high at $168.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Dad's limits are far away: his $130 limit is near the Street's fair value but 25% below market; his sub-$100 limit is 40.6% below - anchored to an old price; nothing triggered.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="10" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="B224" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C224" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D224" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Cloudflare flagged as the single most expensive name in the ~100-stock book: 202x forward P/E, ~860x EV/EBITDA, ~40x sales - priced for flawless execution.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Fastest grower in the cyber group at +34%, expanding into AI-inference at the edge - but a momentum bet, not a value one.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved with CRWD, PANW, ZS and FTNT into a new dedicated Cybersecurity group, making the valuation spread across the five obvious.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="10" t="inlineStr">
-        <is>
-          <t>NET</t>
-        </is>
-      </c>
-      <c r="B225" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C225" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D225" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Cybersecurity into SaaS (each stock sits in one group only), leaving Cybersecurity with four names; reversible on request.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="B226" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C226" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D226" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  PANW, first filed under Chips Manufacturing per the handwritten note, moved into a new Cybersecurity group with CRWD, ZS, NET and FTNT.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Within the cyber group, FTNT and PANW stand out as the profitable, cash-generating incumbents versus 32x-200x forward growth peers with similar ~25-34% growth.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="10" t="inlineStr">
-        <is>
-          <t>RBRK</t>
-        </is>
-      </c>
-      <c r="B227" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C227" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D227" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  RBRK (Rubrik) added to the Cybersecurity group at $80.99 - watchlist only, no money in it.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Jumped 8.4% on Aug 4 when Loop Capital initiated coverage with a Buy and a $100 target.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Still loses money and has negative shareholder equity, so its ROE and debt ratios are shown blank.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Price sources conflicted ($80.99 vs $79.64); $80.99 was used since Google Finance agrees and it matches the reported +8.36% move exactly.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>ZS</t>
-        </is>
-      </c>
-      <c r="B228" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C228" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D228" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ZS added to the board (tipping it to 100 tickers), then moved into the new Cybersecurity group with CRWD, PANW, NET and FTNT.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ ZS is the more reasonable entry of the unprofitable cyber names: best Rule of 40 (56), $960M FCF-positive at breakeven, and already down 58% from its high.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  The group makes the valuation spread obvious: ~32x forward for Zscaler vs ~200x for Cloudflare at similar 25-34% growth.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>BWXT</t>
-        </is>
-      </c>
-      <c r="B229" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C229" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D229" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  BWXT's Aug 3 after-market earnings were picked up by the overnight refresh and merged cleanly - all dashboard checks passed (110 stocks, 47 held, totals unchanged).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  BWXT is crossed out on Dad's note, so it was treated as cancelled and excluded from the buy recommendation.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: CNN quoted BWXT at $205 vs the correct $173.79; the bad source was discarded and prices cross-checked via stockanalysis.com and Google Finance.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="B230" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C230" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D230" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Called the cleanest way to play the nuclear buildout without SMR execution risk: actual uranium, actual profit, +113% EPS growth, ~50% analyst upside (avg target $131).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Not cheap at 60x forward earnings.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Named alongside NEE as the conviction picks for real capital in the energy group; SMR/storage names only as small, sized-to-lose speculation.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="10" t="inlineStr">
-        <is>
-          <t>CCJ</t>
-        </is>
-      </c>
-      <c r="B231" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C231" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D231" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Earnings-related fundamentals refresh on CCJ preserved during a data cleanup; only prices were overridden.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>CEG</t>
-        </is>
-      </c>
-      <c r="B232" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C232" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D232" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  CEG reports earnings Aug 6 (VST, also held, reports Aug 7); advice is to wait for both prints before adding anything on the power/energy side.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ CEG declared a dividend of $0.4265 per share on the morning of Aug 5.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Keep about $5,150 in reserve so a post-earnings selloff in CEG or VST can be bought.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="10" t="inlineStr">
-        <is>
-          <t>LEU</t>
-        </is>
-      </c>
-      <c r="B233" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C233" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D233" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  LEU (Centrus Energy) added to Nuclear Energy at the Aug 7 close $191.37. The only US-owned uranium ENRICHER - makes HALEU fuel for next-gen/small reactors. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Profitable and strategically vital: revenue $474M, 10% net margin, a $4.5B order backlog through 2040, a $900M US government HALEU award, and $1.87B cash.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Expensive and volatile: 88x earnings, negative free cash flow (heavy plant spending), 26% of shares sold short, and it swings hugely - 52-week range $142 to $464. Dropped 5% on earnings then bounced 7% next day.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="B234" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C234" s="12" t="inlineStr">
+      <c r="C276" s="12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
       </c>
-      <c r="D234" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- NNE is one of five of eight nuclear names with essentially no profits or revenue - valuation columns blank; treat as a thematic call option and size it like a venture bet.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t>NNE</t>
-        </is>
-      </c>
-      <c r="B235" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C235" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D235" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- NNE has no reliable 52-week low - it prints fresh lows almost daily, with six conflicting candidates (14.71 to 18.04); the card shows 'range n/a'.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="10" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="B236" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C236" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D236" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  OKLO added to the Energy group as a watchlist name among eight energy additions (SMRs, uranium, solar/storage, a utility), with ~$40K reserved for Energy buys.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Warning: OKLO is one of five names with essentially no profits and little revenue - valuation columns are blank; treat as a thematic call option and size it like a venture bet.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Do not read OKLO at -75% off its high as cheap - down a lot is not cheap with no earnings floor; only small, sized-to-lose speculation (CCJ or NEE for conviction instead).</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="10" t="inlineStr">
-        <is>
-          <t>OKLO</t>
-        </is>
-      </c>
-      <c r="B237" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C237" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D237" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: OKLO was refreshed by the Jul 28 data job but access was denied by Jul 30 - the feed's entitlement list shrank, leaving its stored data stale.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>SMR</t>
-        </is>
-      </c>
-      <c r="B238" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C238" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D238" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- SMR is one of five energy names (with OKLO, NNE, TE, EOSE) with essentially no profits — valuation columns blank; thematic call options to be sized like venture bets.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Warning: do not read OKLO/SMR at -75%/-83% off highs as cheap — down a lot is not the same as cheap when there is no earnings floor underneath.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  For real capital in the group, CCJ or NEE were preferred; the SMR-type names only as small, sized-to-lose speculative positions.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
-        <is>
-          <t>UUUU</t>
-        </is>
-      </c>
-      <c r="B239" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C239" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D239" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  UUUU (Energy Fuels) added to Nuclear Energy at the Aug 6 close $12.90 (rebounded ~10% Aug 7). A US uranium miner that also processes rare-earth elements at its Utah mill. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Strong balance sheet: ~$996M working capital (cash + marketable securities), producing real uranium (865k lbs last quarter, sold at $80/lb) and building a rare-earths plant.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Loses money today: -77% net margin, EPS -$0.34, burning ~$120M cash a year. No P/E - you're buying the uranium/rare-earth theme, not profits. 20% of shares are sold short.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="10" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B240" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C240" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D240" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ VST at $160 flagged as a quality name in the ~4% zone worth a good-til-cancelled limit; a normal down day in an earnings-heavy week could fill it.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="10" t="inlineStr">
-        <is>
-          <t>VST</t>
-        </is>
-      </c>
-      <c r="B241" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C241" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D241" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- VST fell 8.15% to $143.23 - the worst day among the holdings; the drop was confirmed by POEMS and Google Finance against one source claiming $145.46.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VST reports Friday Aug 7 (CEG Aug 6); advice: keep ~$5,150 in reserve and wait for both prints before adding on the power/energy side.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VST moved from Energy to Nuclear Energy group (we own 42 sh, cost $6,078, budget $10,000) - its P&amp;L now reports under Nuclear Energy.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 changes: AXON (Axon Enterprise, NASDAQ - Tasers, body cameras, drones/counter-drone and evidence software for public safety) added to Drone &amp; Defense at the Aug 6, 2026 close 522.46, DOWN 14.28% on the day, header stamped "At close: Aug 6, 2026, 4:00 PM EDT" and confirmed by MarketBeat; note ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="10" t="inlineStr">
-        <is>
-          <t>XE</t>
-        </is>
-      </c>
-      <c r="B242" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C242" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D242" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  XE (X-Energy) deliberately left at Monday's Aug 3 close - no trustworthy fresh close was available; the staleness is disclosed on the dashboard; watchlist only, no position.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy to Nuclear Energy (X-energy is a nuclear/small-reactor developer, so it belongs there). Group label only.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B243" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C243" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: ETN's small intraday price drift was refreshed on the dashboard.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B244" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C244" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D244" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The $300 buy limit sits below Eaton's 52-week low of $311.92 - it waits for ground untouched in a year; analyst average is $455.79, 52% above the desired entry.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Checksum caught a transcription error: ETN was keyed 386.20 vs actual 386.26; fixed, and earnings-related fundamentals refresh on ETN preserved.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="B245" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C245" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  ETN (19 shares, $7,879.55 cost) moved from Energy into the new 'Power and Electrification' group; totals unchanged to the cent.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="10" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C246" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Order-list query: item 8 read as COIN, but a $300 limit vs a $164 price makes no sense; GEV (closed $981.98) noted as one possible intended ticker.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="10" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="B247" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C247" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D247" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  GEV (2 shares, $2,147.30 cost) moved with ETN into a new Power and Electrification group; totals unchanged to the cent, nothing bought or sold.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- GE Vernova JV partner AirJoule: genuinely operating (unit installed Jul 28, Kubota deal Jul 21) but no revenue, 16 employees and a $46M funding hole - a ticket, not a position.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="10" t="inlineStr">
-        <is>
-          <t>HUBB</t>
-        </is>
-      </c>
-      <c r="B248" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C248" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D248" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Hubbell was pulled fresh onto the dashboard and joined the new Power &amp; Electrification group as a watchlist name at $502.24.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ It beat and raised on grid modernization and data centres - the steadiest, lowest-volatility of the four new power names.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  None of Dad's nine buy limits are triggered; Hubbell is the closest, still 14.4% above his $430 line, with about +20% to the analyst target.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="10" t="inlineStr">
-        <is>
-          <t>HYLN</t>
-        </is>
-      </c>
-      <c r="B249" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C249" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D249" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  HYLN (Hyliion) added to Power &amp; Electrification at the Aug 7 close $3.87. Makes the KARNO generator - a fuel-flexible power module. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: Pre-revenue in practice: only $5.8M sales, so its price-to-sales (121x) is meaningless and it burns ~$64M/yr. Very volatile (beta 3.6). A bet on a technology, not a business yet.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Momentum from defence: won a $41.7M US Navy award to scale its power modules and demonstrated them running as one plant. $72M cash. 3 analysts Buy, avg $7. Q2 call Aug 12.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B250" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C250" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D250" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: moved to the Energy group per the handwritten note ($5K budget) and small intraday price drifts refreshed.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C251" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D251" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: Advisor admitted MPWR's 'live' price was filled in from memory, not retrieved; on a proper re-pull, four of five such prices were wrong.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Jumped 10.6% overnight, blowing straight through the standing buy limit - the entry moved further away.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Earnings-related fundamentals refresh on MPWR preserved during a data cleanup.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="10" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="B252" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C252" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D252" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Energy group cleaned up: MPWR now sits in a tighter 12-name electrification-and-power bucket with ETN, VRT, GEV, VST, NEE.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MPWR moved from Energy to Power &amp; Electrification group (we own 1 sh, cost $1,538.56, budget $5,000) - its P&amp;L now reports under Power &amp; Electrification. It makes power-management chips for AI/data-centre boards.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 move: MPWR (Monolithic Power Systems, HELD - 1 sh / 1,538.56 cost / 5,000 budget) moved Energy -&gt; Power and Electrification per request. Field values, position and budget untouched; group P&amp;L attribution now reports under Power and Electrification. Energy 11 -&gt; 10 names, Power and ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="10" t="inlineStr">
-        <is>
-          <t>NVT</t>
-        </is>
-      </c>
-      <c r="B253" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C253" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NVT (nVent Electric) added at $162.24 as watchlist-only in the new six-name Power and Electrification group (which also absorbed held positions ETN and GEV).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ nVent has raised full-year guidance twice on AI liquid-cooling demand and is buying back its own shares.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: sources disagreed on the close ($162.24 vs $163.68); $162.24 was stored on a two-sources-to-one basis.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="10" t="inlineStr">
-        <is>
-          <t>POWI</t>
-        </is>
-      </c>
-      <c r="B254" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C254" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D254" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  POWI (Power Integrations) added to Power &amp; Electrification at the Aug 7 close $64.59. Makes energy-efficient power-conversion chips for industry, renewables and AI. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Rock-solid balance sheet (no debt, pays a dividend), 54% gross margins, and Q2 beat and jumped ~9%. A quality niche chipmaker levered to grid/renewables demand.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Barely profitable right now, so the P/E (147) and EV/EBITDA (80) look extreme; you're paying up for a recovery. Only 5 analysts, avg target $77. Stock $65 vs a $91 high.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="10" t="inlineStr">
-        <is>
-          <t>POWL</t>
-        </is>
-      </c>
-      <c r="B255" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C255" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D255" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Powell Industries missed on both revenue and profit Aug 3, gapping down almost 13% before closing -3.8%; with only four analysts covering it, the price moves violently.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ The order book tells the opposite story: new orders +158%, backlog +69%, and a 3.0x book-to-bill - three dollars booked for every dollar shipped.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Watchlist-only in the new Power &amp; Electrification group at $211.38; an implausible 122.6% return-on-capital figure was rejected for the conservative 38.4%.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="10" t="inlineStr">
-        <is>
-          <t>PWR</t>
-        </is>
-      </c>
-      <c r="B256" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C256" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D256" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  PWR added watchlist-only to the new 'Power and Electrification' group alongside POWL, NVT and HUBB.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ Quanta Services ($693) beat big on Jul 30 and raised full-year guidance - revenue +41%, backlog $53.4B; the stock jumped 13.65% that day.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="10" t="inlineStr">
-        <is>
-          <t>AIRJ</t>
-        </is>
-      </c>
-      <c r="B257" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C257" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- AIRJ is filed under Energy but is really an industrial equipment maker (atmospheric water capture); a lottery ticket, and its news is about drinking water, not energy.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Real traction: 50/50 JV with GE Vernova is operating (unit installed at GE's NY campus Jul 28); Kubota signed as exclusive US residential partner Jul 21, stock +15% that day.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Balance sheet is clean: $35M cash, no debt, funded into 2028; all five covering analysts have targets above the price (lowest $6.00 vs $5.95).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- But there is no revenue at all - advisor's verdict: interesting, not a buy today.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Data caveat: the $5.84 Aug 4 close comes from a single source; no second source had that day's data.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Housekeeping: AIRJ was already in Energy, so the regrouping request needed no action.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="10" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="B258" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C258" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D258" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="10" t="inlineStr">
-        <is>
-          <t>FLNC</t>
-        </is>
-      </c>
-      <c r="B259" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C259" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D259" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">RED FLAG: FLNC missed Q3 badly on Aug 5: revenue $649.8M vs $806.2M expected (-19.4%), EPS -$0.24 vs +$0.02, full-year guidance cut to $2.9-3.1B from $3.2-3.6B; shares fell to ~$10.89.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Verdict: a falling knife — do not buy; analysts will cut forecasts and the stock likely has further to fall.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- The $14.23 stored on the dashboard is the pre-release close and is stale; sources also disagree on FLNC's market cap ($1.43B-$2.62B), EPS, ROE and net margin.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  FLNC had just been added to the Energy group at the Aug 5 close of $14.23 before the report; the next refresh will capture the gap down.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="10" t="inlineStr">
-        <is>
-          <t>MYRG</t>
-        </is>
-      </c>
-      <c r="B260" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C260" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D260" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MYRG (MYR Group - you wrote 'MYR') added to the new Renewal Energy group at the Aug 7 close $337.42. An electrical-infrastructure builder: power lines, substations and data-centre/grid electrical work. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ High quality and profitable: revenue $4B (+16%), earnings more than doubled to $10.54/share, 25% return on capital, positive cash flow, almost no debt. Record Q2 and record $3.16B backlog.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Direct beneficiary of the grid buildout and data-centre electrification wave. Analysts see meaningful upside (avg ~$423 vs ~$337). Trades at a reasonable ~26x forward earnings for the growth.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- A contractor, so margins are thin (~4% net) and results can be lumpy project to project; the stock has pulled back from a $503 high.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="10" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B261" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C261" s="14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D261" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ NEE is the only dividend-quality name in the group: a $187B regulated utility plus the largest US renewables developer, 32% margins, near the ~$99 analyst fair value.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>+ For real capital in the nuclear/energy group: CCJ or NEE for conviction; the SMR and storage names only as small, sized-to-lose speculative bets.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>NEE</t>
-        </is>
-      </c>
-      <c r="B262" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C262" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D262" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NEE now sits in the cleaner electrification-and-power-equipment bucket (with ETN, VRT, GEV, VST, MPWR) after the Energy group was trimmed from 18 names to 12.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="10" t="inlineStr">
-        <is>
-          <t>NRG</t>
-        </is>
-      </c>
-      <c r="B263" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C263" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  NRG (NRG Energy) added to Energy at the Aug 6 close $119.05. A big Texas power company - it generates electricity, sells it to homes, and is now a major play on data-centre/AI power demand. Watchlist only.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Real, profitable business paying a ~1.6% dividend: $33B revenue, earnings up 76% to $3.87/share, 24% return on equity. Cheap on next year's earnings (~12x) with a bargain PEG of 0.5.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Growth catalyst: on its Aug 4 call it announced a landmark 1.2-gigawatt deal (expandable to 2.4GW) to power a hyperscaler's data centre in Texas - ~$500M/yr of profit once running, ~2029.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Heavily indebted (debt is ~5x equity - normal for a utility but real), and free cash flow is thin, so it looks expensive on a cash-flow basis (72x). Management sees this year's profit below the mid-point on soft Texas power prices.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Analysts still like it (~$194 avg target vs $119 now) but two firms trimmed targets on Aug 5; the stock touched a 52-week low ($112.50) recently. The $119.05 stored is the Aug 6 close - tonight's refresh confirms it.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  (new, not yet condensed) Aug 7 additions (both watchlist only - no position, no budget): (1) NRG (NRG Energy, NYSE) added to Energy at the Aug 6, 2026 close 119.05. Both stockanalysis and MarketBeat quote pages were in a LIVE Aug 7 session at fetch, so 119.05 is the stockanalysis 'Previous Close' field, not a verbatim 4:00 ...</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B264" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C264" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D264" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- VRT reports earnings within a week - buying now means holding a binary event within days, which is why the week's buy pick went elsewhere.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Per-firm analyst rating actions for mid-caps like VRT need the FMP Starter plan (~$22-29/month); the upgrade was recommended as worthwhile.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B265" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C265" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D265" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VRT cited as part of the AI-rack exposure (with NVDA, AVGO, ANET, CRDO) that all rely on Amphenol connectors - context for the APH pick-and-shovel case.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="inlineStr">
-        <is>
-          <t>VRT</t>
-        </is>
-      </c>
-      <c r="B266" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C266" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D266" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  VRT now sits in the cleaner electrification-and-power-equipment bucket after the Energy group regrouping (18 names down to 12).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved from Energy into the new Renewal Energy group. (Group label only - no change to any figures.)</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="10" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="B267" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C267" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D267" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Affirm screens at 19x forward earnings with +32% growth and a 10% margin; it has only just turned profitable and carries buy-now-pay-later credit risk.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Advisor files Affirm with the momentum-and-story names (Coinbase, Robinhood, Shopify), not the quality bucket - valuation has a long way to fall if growth blinks.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="10" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="B268" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C268" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D268" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="10" t="inlineStr">
-        <is>
-          <t>MELI</t>
-        </is>
-      </c>
-      <c r="B269" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C269" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D269" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  MELI appears among the pre-dashboard closed exits (with TTD, APP, SOFI, HOOD) captured in the new group P&amp;L view.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="10" t="inlineStr">
-        <is>
-          <t>MELI</t>
-        </is>
-      </c>
-      <c r="B270" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C270" s="13" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="D270" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Verdict: parked, not rejected - it reported the night before, fell 4.5% with margins down 550bps; same timing trap as APP, revisit in a week once the dust settles.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">+ Still the most attractive fundamentals of the candidate list: the cheapest cash flow of the lot at $1,922.57 with +15% upside shown and revenue growing 50%.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">- Risk: MELI fell because its numbers got worse - when analysts update they will cut forecasts, so the stock likely has further to adjust downward.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="10" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-20  (Jul 20-26, 2026)</t>
-        </is>
-      </c>
-      <c r="C271" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D271" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>- Great business but priced for perfection at 84x EV/EBITDA with +32% growth; bucketed with the momentum-and-story names where valuation has far to fall if growth blinks.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="10" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="B272" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C272" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D272" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Moved into the new Digital Applications group (from Fintech/Digital Platform). Group label only - no change to any figures or position.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="10" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B273" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-27  (Jul 27 - Aug 02, 2026)</t>
-        </is>
-      </c>
-      <c r="C273" s="13" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="D273" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  Uber is one of 12 watchlist-only names occupying the free data feed's whitelist while $242K of actual holdings goes unpriced - an entitlement quirk, not a stock view.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="10" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="B274" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-03  (Aug 03-09, 2026)</t>
-        </is>
-      </c>
-      <c r="C274" s="12" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D274" s="10" t="inlineStr">
+      <c r="D276" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20125,8 +20508,243 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="10" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="B277" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C277" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D277" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  WDAY (Workday) added to Digital Applications at the Aug 7 close $179.64. Cloud software for HR and finance departments. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Cash-rich, not earnings-poor: the headline P/E (56) looks high on accounting profit, but on cash terms it's cheap (forward P/E 16, PEG 0.76, $3B free cash flow). Steady ~13% growth.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- 11% of shares are shorted, the founder returned as CEO with layoffs in Feb, and analysts' avg target ($169) sits below today's price. Reports Aug 27.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B278" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C278" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D278" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  CAT (Caterpillar) added to the new Industrial STX group at the Aug 7 close $842.19. The world's biggest construction and mining equipment maker; also a data-centre-power beneficiary. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Firing on all cylinders: revenue +18%, 57% return on equity, record backlog; Q2 beat and jumped ~9%. Pays a small dividend. 28 analysts Buy, avg ~$973.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Cyclical and richly valued (P/E 36); already pulled back ~21% from its June peak of ~$1,073, so it can be volatile.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B279" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C279" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D279" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  DE (Deere) added to Industrial STX at the Aug 7 close $620.83. The world's largest maker of farm machinery, plus construction equipment. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">- In a farming downturn right now: earnings down ~15% and low returns on capital this year, though management expects agriculture to bottom in 2026.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>+ Still a dominant franchise with pricing power; 24 analysts rate it Buy, avg ~$648. Reports Aug 20. A recovery play if the ag cycle turns.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C280" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  GE (GE Aerospace) added to Industrial STX at the Aug 7 close $370.08. This is the jet-engine company left after GE split into three in 2024 - NOT the old conglomerate. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Best-in-class: revenue +22%, 31% return on capital, strong cash flow; Q2 beat and raised full-year guidance. 22 analysts rate it STRONG BUY (avg ~$405) - the highest conviction of these four industrials.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Priced for perfection at 44x earnings and sits near its all-time high, so limited margin for error.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="10" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="B281" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-03  (Aug 03-09, 2026)</t>
+        </is>
+      </c>
+      <c r="C281" s="13" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="D281" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  MMM (3M) added to Industrial STX at the Aug 7 close $182.90. A diversified industrial (tapes, abrasives, safety, electronics) recovering after big legal settlements. Watchlist only.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">+ Turnaround underway: Q2 beat, best organic growth in 5 years, raised full-year guidance; pays a 1.7% dividend. 37% return on capital.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>- Near its 52-week high with the average analyst target (~$182) essentially at today's price - limited upside priced in - and heavy debt from PFAS/earplug settlements. Views are split (3 Sells).</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D274"/>
+  <autoFilter ref="A1:D281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -52612,7 +53230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -53453,8 +54071,25 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>7c56e84</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Aug 8: created new group 'Digital Applications' (g19, colour slot --s20 added to both themes) and MOVED MELI, SHOP, AFRM and UBER into it from Fintech / Digital Platform (all watchlist, no positions; field values untouched, group P&amp;L re-attributed). Rationale: these four are consumer app/marketplace platforms (MercadoLibre e-commerce+fintech, Shopify merchant software, Affirm buy-now-pay-later, Uber mobility/delivery) as distinct from the pure payment networks left in Fintech / Digital Platform. Fintech / Digital Platform 15 -&gt; 11 names (V, MA, PYPL, FI, COIN, HOOD, SOFI, NU, SE, LMND, SOUN); Digital Applications new = 4. Total groups 19 -&gt; 20.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C49"/>
+  <autoFilter ref="A1:C50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
